--- a/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>YETI</t>
   </si>
@@ -656,392 +656,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44562</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44198</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43827</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43463</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43099</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>519800</v>
+      </c>
+      <c r="E8" s="3">
         <v>433600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>402600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>302800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>448000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>433600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>420000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>293600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>443100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>362600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>357700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>247600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>375800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>294600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>246900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>174400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>297600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>229100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>231700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>155400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>241200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>196100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>206300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>135300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>202100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>183000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>148400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>204600</v>
+      </c>
+      <c r="E9" s="3">
         <v>182300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>187700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>140900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>281000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>211100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>200900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>138800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>188300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>155600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>148600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>102400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>150900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>120600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>109400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>82000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>135300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>109000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>115400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>78700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>113400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>98600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>105700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>78100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>109000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>100800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>75400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>315200</v>
+      </c>
+      <c r="E10" s="3">
         <v>251300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>214900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>161900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>167000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>222500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>219100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>154800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>254800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>207000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>209200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>145200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>224900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>174000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>137500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>92400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>162300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>120100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>116300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>76700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>127800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>97500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>100600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>57200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>93100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>82200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>73000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1072,8 +1084,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1158,8 +1171,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1244,8 +1260,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1330,8 +1349,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1416,8 +1438,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1445,180 +1470,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>421600</v>
+      </c>
+      <c r="E17" s="3">
         <v>371700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>352200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>287700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>491700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>365100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>351700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>260300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>349400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>293900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>285200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>207500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>294300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>224500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>158300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>285600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>195100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>196700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>146600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>203600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>168000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>173100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>132000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>178200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>158300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>130700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E18" s="3">
         <v>61900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>50400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-43700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>68500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>68300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>33300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>93700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>68700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>72500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>40100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>81500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>70100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>46500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>16200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>34000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>35000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>37600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>28100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>33200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>23900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>24700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>17700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1649,203 +1681,210 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>6500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-7300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-100</v>
       </c>
       <c r="Z20" s="3">
         <v>-100</v>
       </c>
       <c r="AA20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>115100</v>
+      </c>
+      <c r="E21" s="3">
         <v>69000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>63400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-25900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>71200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>72400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>42800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>101700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>76000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>78900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>47300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>90300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>77500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>55100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>22000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>19200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>41100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>42300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>15400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>43200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>34200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>39300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>8900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>28900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>30600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>23500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>800</v>
       </c>
       <c r="K22" s="3">
         <v>800</v>
@@ -1857,230 +1896,239 @@
         <v>800</v>
       </c>
       <c r="N22" s="3">
+        <v>800</v>
+      </c>
+      <c r="O22" s="3">
         <v>900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>8600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>8400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>8100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E23" s="3">
         <v>57600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>50800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>14500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-38500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>59700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>61600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>33400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>92200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>66700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>70600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>38900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>81100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>68100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>44800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>11200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>28400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>29400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>29900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>20200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>24500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>14700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>16500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E24" s="3">
         <v>14900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-10800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>19300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>13700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>18800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>16600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>11300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>7100</v>
       </c>
       <c r="U24" s="3">
         <v>7100</v>
       </c>
       <c r="V24" s="3">
+        <v>7100</v>
+      </c>
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2165,180 +2213,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E26" s="3">
         <v>42700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>38100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-27700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>45500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>46300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>25700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>72900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>53000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>56200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>30500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>62400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>51400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>33500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>21300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>22200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>25200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>17000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>18800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>9700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>11300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E27" s="3">
         <v>42700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>38100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-27700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>45500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>46300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>25700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>72900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>53000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>56200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>30500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>62400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>51400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>33500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>21300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>22200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>25200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>17000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>18800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>9700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>11300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2423,8 +2480,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2479,17 +2539,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2497,20 +2557,23 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2595,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2681,180 +2747,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E32" s="3">
         <v>4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-6500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>7300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>100</v>
       </c>
       <c r="Z32" s="3">
         <v>100</v>
       </c>
       <c r="AA32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E33" s="3">
         <v>42700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>38100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-27700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>45500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>46300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>25700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>72900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>53000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>56200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>30500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>62400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>51400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>33500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>21300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>22200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>25200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>17000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>18800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>11300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>7000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2939,185 +3014,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E35" s="3">
         <v>42700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>38100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-27700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>45500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>46300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>25700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>72900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>53000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>56200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>30500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>62400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>51400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>33500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>21300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>22200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>25200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>17000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>18800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>11300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>7000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44562</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44198</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43827</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43463</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43099</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3148,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3180,94 +3265,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>439000</v>
+      </c>
+      <c r="E41" s="3">
         <v>281400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>223100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>167800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>234700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>77800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>92000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>100300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>312200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>259300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>233800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>190300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>253300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>234800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>127500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>118200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>72500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>34600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>38000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>80100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>52100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>71300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>60400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>53700</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3352,352 +3441,367 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>95800</v>
+      </c>
+      <c r="E43" s="3">
         <v>127900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>131600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>95600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>79400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>93900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>94300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>83000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>109500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>83300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>81900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>67100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>65400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>71200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>85900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>60200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>82700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>74800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>75900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>63000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>59300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>61900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>65400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>60400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>67200</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>337200</v>
+      </c>
+      <c r="E44" s="3">
         <v>341300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>322000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>347000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>371400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>439400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>490000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>413000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>318900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>266000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>221700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>183900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>140100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>134600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>138800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>202400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>185700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>209200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>181400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>164300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>145400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>157700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>149400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>158500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>175100</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E45" s="3">
         <v>40700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>45200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>44500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>40800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>39600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>23600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>24500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>19900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>19600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>20100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>13000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>11100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7100</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>914400</v>
+      </c>
+      <c r="E46" s="3">
         <v>791300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>721900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>654900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>718900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>644700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>717000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>635900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>770200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>632200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>561200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>465700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>476500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>454700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>367400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>400600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>360500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>331800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>313000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>266400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>297000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>284600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>297300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>289900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>303000</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3782,180 +3886,189 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>208300</v>
+      </c>
+      <c r="E48" s="3">
         <v>192600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>189500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>179300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>180000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>183700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>183800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>179700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>174000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>163000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>153700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>119100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>112200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>110000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>112300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>116300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>120400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>81200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>80000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>78200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>74100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>72400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>71100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>71500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>73800</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>171900</v>
+      </c>
+      <c r="E49" s="3">
         <v>168400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>165200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>155100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>153700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>152400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>152100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>151400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>149600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>148400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>147200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>146500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>146400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>145900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>145800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>145700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>145100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>145000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>144700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>144300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>134300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>135400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>133700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>130300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>128600</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4040,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4126,94 +4242,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E52" s="3">
         <v>3500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2500</v>
       </c>
       <c r="J52" s="3">
         <v>2500</v>
       </c>
       <c r="K52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L52" s="3">
         <v>2600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1900</v>
-      </c>
-      <c r="O52" s="3">
-        <v>2000</v>
       </c>
       <c r="P52" s="3">
         <v>2000</v>
       </c>
       <c r="Q52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R52" s="3">
         <v>1900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4298,94 +4420,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1297200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1155900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1085400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1006500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1076800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>983200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1055400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>969500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1096400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>945500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>864000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>733300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>737100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>712600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>627500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>666800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>629500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>559700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>540400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>495800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>514200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>502600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>510400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>502200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>516400</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4416,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4448,114 +4577,118 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>190400</v>
+      </c>
+      <c r="E57" s="3">
         <v>179100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>143400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>101700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>140800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>122800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>204100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>167400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>191300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>166100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>145700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>120000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>123600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>101900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>41400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>74400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>83800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>105500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>101500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>78200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>68700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>76900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>73500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>51600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>40300</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E58" s="3">
         <v>6500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>24400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>24600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>24600</v>
       </c>
       <c r="J58" s="3">
         <v>24600</v>
@@ -4564,43 +4697,43 @@
         <v>24600</v>
       </c>
       <c r="L58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="M58" s="3">
         <v>24500</v>
       </c>
       <c r="N58" s="3">
-        <v>22700</v>
+        <v>24500</v>
       </c>
       <c r="O58" s="3">
         <v>22700</v>
       </c>
       <c r="P58" s="3">
+        <v>22700</v>
+      </c>
+      <c r="Q58" s="3">
         <v>20800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>18900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>17100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>15200</v>
-      </c>
-      <c r="T58" s="3">
-        <v>42100</v>
       </c>
       <c r="U58" s="3">
         <v>42100</v>
       </c>
       <c r="V58" s="3">
-        <v>43600</v>
+        <v>42100</v>
       </c>
       <c r="W58" s="3">
         <v>43600</v>
       </c>
       <c r="X58" s="3">
-        <v>47100</v>
+        <v>43600</v>
       </c>
       <c r="Y58" s="3">
         <v>47100</v>
@@ -4611,8 +4744,8 @@
       <c r="AA58" s="3">
         <v>47100</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
+      <c r="AB58" s="3">
+        <v>47100</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>8</v>
@@ -4620,352 +4753,367 @@
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>201400</v>
+      </c>
+      <c r="E59" s="3">
         <v>175200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>195300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>203700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>243600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>128400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>162700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>158100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>187800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>139200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>133800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>110300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>141400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>96900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>70800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>59100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>71300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>53400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>54500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>50600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>75000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>62100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>52100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>51900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>64500</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>398400</v>
+      </c>
+      <c r="E60" s="3">
         <v>360800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>344900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>329800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>409000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>275600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>391400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>350100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>403700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>329900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>304000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>253000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>287800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>219600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>131200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>150600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>170300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>201100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>198200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>172500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>187300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>186000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>172600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>150600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>151900</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E61" s="3">
         <v>79500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>81100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>65700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>71700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>77800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>83600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>89600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>95700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>101700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>107800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>105500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>111000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>215800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>270800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>326300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>281700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>252700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>263300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>273800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>284400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>340700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>380800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>418000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>428600</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>96600</v>
+      </c>
+      <c r="E62" s="3">
         <v>76700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>72200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>68400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>69500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>79200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>80500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>83500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>79100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>74300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>68100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>53400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>49900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>54600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>56400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>58300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>55500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>15100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>14000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>13800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>12600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>12100</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5050,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5136,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5222,94 +5376,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>573600</v>
+      </c>
+      <c r="E66" s="3">
         <v>517100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>498200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>464000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>550300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>432600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>555500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>523200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>578500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>505900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>479900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>412000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>448600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>489900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>458400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>535100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>507500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>471800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>476500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>460300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>485200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>539800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>567200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>581200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>592700</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5340,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5426,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5512,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5598,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5684,94 +5854,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>438400</v>
+      </c>
+      <c r="E72" s="3">
         <v>359800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>317200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>279100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>268600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>296300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>250800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>204500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>178900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>106000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>53000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-33700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-96100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-147600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-181100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-189500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-194300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-215500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-237600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-240100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-265100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-281800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-300000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-296200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5856,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5942,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6028,94 +6210,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>723600</v>
+      </c>
+      <c r="E76" s="3">
         <v>638800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>587200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>542600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>526500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>550700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>499900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>446400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>517800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>439600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>384100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>321300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>288400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>222600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>169000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>131600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>122000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>87900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>64000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>35500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>29000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-56800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-79000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-76200</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6200,185 +6388,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44562</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44198</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43827</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43463</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43099</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E81" s="3">
         <v>42700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>38100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-27700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>45500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>46300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>25700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>72900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>53000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>56200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>30500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>62400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>51400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>33500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>21300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>22200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>25200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>17000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>18800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>11300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>7000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6409,52 +6606,53 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E83" s="3">
         <v>11200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>7700</v>
       </c>
       <c r="R83" s="3">
         <v>7700</v>
@@ -6463,40 +6661,43 @@
         <v>7700</v>
       </c>
       <c r="T83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="U83" s="3">
         <v>7400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>6500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>6600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>6300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>5700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>5600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>4600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6581,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6667,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6753,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6839,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6925,94 +7138,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>171200</v>
+      </c>
+      <c r="E89" s="3">
         <v>86000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>75500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-46700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>173100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-88600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>73300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>51000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>62500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-40300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>127300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>166700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>68500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>60300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>16800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>39800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-30000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>57200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>35200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>58300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>25300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>72200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>65600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>21600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-16100</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7043,94 +7262,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7500</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-8400</v>
       </c>
       <c r="V91" s="3">
         <v>-8400</v>
       </c>
       <c r="W91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="X91" s="3">
         <v>-7500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7215,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7301,94 +7527,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-26300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-17800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-18100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-19800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7419,8 +7651,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7473,11 +7706,11 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-600</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -7505,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7591,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7677,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7763,157 +8005,163 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-107600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-102800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-53500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-52600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>45700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-12900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-11100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-10600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-11100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-21500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-45100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-37900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>18300</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
@@ -7924,101 +8172,107 @@
         <v>0</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>157600</v>
+      </c>
+      <c r="E102" s="3">
         <v>58200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>55300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-66900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>157000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-211900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>52900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>25500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>43500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-63000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>18500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>107300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>45700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>38000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>19000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-61000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>28000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-19200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>10900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>18900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>19400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-9700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
   <si>
     <t>YETI</t>
   </si>
@@ -656,404 +656,417 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44562</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44198</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43827</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43463</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43099</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>341400</v>
+      </c>
+      <c r="E8" s="3">
         <v>519800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>433600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>402600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>302800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>448000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>433600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>420000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>293600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>443100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>362600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>357700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>247600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>375800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>294600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>246900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>174400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>297600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>229100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>231700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>155400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>241200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>196100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>206300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>135300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>202100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>183000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>148400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>146600</v>
+      </c>
+      <c r="E9" s="3">
         <v>204600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>182300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>187700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>140900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>281000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>211100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>200900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>138800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>188300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>155600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>148600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>102400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>150900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>120600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>109400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>82000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>135300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>109000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>115400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>78700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>113400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>98600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>105700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>78100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>109000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>100800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>75400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>194800</v>
+      </c>
+      <c r="E10" s="3">
         <v>315200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>251300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>214900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>161900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>167000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>222500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>219100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>154800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>254800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>207000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>209200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>145200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>224900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>174000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>137500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>92400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>162300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>120100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>116300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>76700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>127800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>97500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>100600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>57200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>93100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>82200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>73000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1085,8 +1098,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1174,8 +1188,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,8 +1280,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1352,8 +1372,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1441,8 +1464,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1497,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>315600</v>
+      </c>
+      <c r="E17" s="3">
         <v>421600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>371700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>352200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>287700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>491700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>365100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>351700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>260300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>349400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>293900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>285200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>207500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>294300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>224500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>200400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>158300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>285600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>195100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>196700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>146600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>203600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>168000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>173100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>132000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>178200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>158300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>130700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E18" s="3">
         <v>98200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>61900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>50400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-43700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>68500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>68300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>33300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>93700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>68700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>72500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>40100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>81500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>70100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>46500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>16200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>34000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>35000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>37600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>28100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>33200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>23900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>24700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>17700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,212 +1715,219 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E20" s="3">
         <v>4900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>6500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-7300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-100</v>
       </c>
       <c r="AA20" s="3">
         <v>-100</v>
       </c>
       <c r="AB20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E21" s="3">
         <v>115100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>69000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>63400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>26500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-25900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>71200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>72400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>42800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>101700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>76000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>78900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>47300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>90300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>77500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>55100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>22000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>19200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>41100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>42300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>15400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>43200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>34200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>39300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>8900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>28900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>30600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>23500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>800</v>
       </c>
       <c r="L22" s="3">
         <v>800</v>
@@ -1899,236 +1939,245 @@
         <v>800</v>
       </c>
       <c r="O22" s="3">
+        <v>800</v>
+      </c>
+      <c r="P22" s="3">
         <v>900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>6800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>8600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>8400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E23" s="3">
         <v>103000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>57600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>50800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-38500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>59700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>61600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>33400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>92200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>66700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>70600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>38900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>81100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>68100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>44800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>11200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>28400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>29400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>29900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>20200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>24500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>14700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>16500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>10900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E24" s="3">
         <v>24400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-10800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>13700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>18800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>16600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>7100</v>
       </c>
       <c r="V24" s="3">
         <v>7100</v>
       </c>
       <c r="W24" s="3">
+        <v>7100</v>
+      </c>
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2265,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E26" s="3">
         <v>78600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>42700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>38100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-27700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>45500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>46300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>25700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>72900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>53000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>56200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>30500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>62400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>51400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>33500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>8500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>21300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>22200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>25200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>17000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>18800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>9700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>11300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E27" s="3">
         <v>78600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>42700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>38100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-27700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>45500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>46300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>25700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>72900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>53000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>56200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>30500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>62400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>51400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>33500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>21300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>22200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>25200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>17000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>18800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>9700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>11300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2541,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2542,17 +2603,17 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2560,20 +2621,23 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2725,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,186 +2817,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-6500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>7300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>100</v>
       </c>
       <c r="AA32" s="3">
         <v>100</v>
       </c>
       <c r="AB32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC32" s="3">
         <v>600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E33" s="3">
         <v>78600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>42700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>38100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-27700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>45500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>46300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>25700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>72900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>53000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>56200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>30500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>62400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>51400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>33500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>21300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>22200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>25200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>17000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>18800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>11300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3093,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E35" s="3">
         <v>78600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>42700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>38100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-27700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>45500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>46300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>25700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>72900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>53000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>56200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>30500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>62400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>51400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>33500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>21300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>22200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>25200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>17000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>18800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>11300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44562</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44198</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43827</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43463</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43099</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3318,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,97 +3352,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>173900</v>
+      </c>
+      <c r="E41" s="3">
         <v>439000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>281400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>223100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>167800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>234700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>77800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>92000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>100300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>312200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>259300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>233800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>190300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>253300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>234800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>127500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>118200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>72500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>34600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>38000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>19000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>80100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>52100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>71300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>60400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>53700</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3444,364 +3534,379 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>108400</v>
+      </c>
+      <c r="E43" s="3">
         <v>95800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>127900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>131600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>95600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>79400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>93900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>94300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>83000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>109500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>83300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>81900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>67100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>65400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>71200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>85900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>60200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>82700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>74800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>75900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>63000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>59300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>61900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>65400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>60400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>67200</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>363900</v>
+      </c>
+      <c r="E44" s="3">
         <v>337200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>341300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>322000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>347000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>371400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>439400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>490000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>413000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>318900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>266000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>221700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>183900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>140100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>134600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>138800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>202400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>185700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>209200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>181400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>164300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>145400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>157700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>149400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>158500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>175100</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E45" s="3">
         <v>42500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>40700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>45200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>44500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>40800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>39600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>24500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>19900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>19600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>20100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>13000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>11100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>10500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7100</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>703200</v>
+      </c>
+      <c r="E46" s="3">
         <v>914400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>791300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>721900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>654900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>718900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>644700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>717000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>635900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>770200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>632200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>561200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>465700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>476500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>454700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>367400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>400600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>360500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>331800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>313000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>266400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>297000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>284600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>297300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>289900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>303000</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3889,186 +3994,195 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>207100</v>
+      </c>
+      <c r="E48" s="3">
         <v>208300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>192600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>189500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>179300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>180000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>183700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>183800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>179700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>174000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>163000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>153700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>119100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>112200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>110000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>112300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>116300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>120400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>81200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>80000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>78200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>74100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>72400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>71100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>71500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>73800</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>206800</v>
+      </c>
+      <c r="E49" s="3">
         <v>171900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>168400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>165200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>155100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>153700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>152400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>152100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>151400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>149600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>148400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>147200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>146500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>146400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>145900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>145800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>145700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>145100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>145000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>144700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>144300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>134300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>135400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>133700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>130300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>128600</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4270,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,97 +4362,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E52" s="3">
         <v>2600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>24100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>2500</v>
       </c>
       <c r="K52" s="3">
         <v>2500</v>
       </c>
       <c r="L52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M52" s="3">
         <v>2600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1900</v>
-      </c>
-      <c r="P52" s="3">
-        <v>2000</v>
       </c>
       <c r="Q52" s="3">
         <v>2000</v>
       </c>
       <c r="R52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S52" s="3">
         <v>1900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11000</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4546,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1119800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1297200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1155900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1085400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1006500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1076800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>983200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1055400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>969500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1096400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>945500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>864000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>733300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>737100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>712600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>627500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>666800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>629500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>559700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>540400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>495800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>514200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>502600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>510400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>502200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>516400</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4674,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,120 +4708,124 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>139100</v>
+      </c>
+      <c r="E57" s="3">
         <v>190400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>179100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>143400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>101700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>140800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>122800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>204100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>167400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>191300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>166100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>145700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>120000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>123600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>101900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>41400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>74400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>83800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>105500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>101500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>78200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>68700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>76900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>73500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>51600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>40300</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E58" s="3">
         <v>6600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>24400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>24400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>24600</v>
       </c>
       <c r="K58" s="3">
         <v>24600</v>
@@ -4700,43 +4834,43 @@
         <v>24600</v>
       </c>
       <c r="M58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="N58" s="3">
         <v>24500</v>
       </c>
       <c r="O58" s="3">
-        <v>22700</v>
+        <v>24500</v>
       </c>
       <c r="P58" s="3">
         <v>22700</v>
       </c>
       <c r="Q58" s="3">
+        <v>22700</v>
+      </c>
+      <c r="R58" s="3">
         <v>20800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>18900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>17100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>15200</v>
-      </c>
-      <c r="U58" s="3">
-        <v>42100</v>
       </c>
       <c r="V58" s="3">
         <v>42100</v>
       </c>
       <c r="W58" s="3">
-        <v>43600</v>
+        <v>42100</v>
       </c>
       <c r="X58" s="3">
         <v>43600</v>
       </c>
       <c r="Y58" s="3">
-        <v>47100</v>
+        <v>43600</v>
       </c>
       <c r="Z58" s="3">
         <v>47100</v>
@@ -4747,8 +4881,8 @@
       <c r="AB58" s="3">
         <v>47100</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
+      <c r="AC58" s="3">
+        <v>47100</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>8</v>
@@ -4756,364 +4890,379 @@
       <c r="AE58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>153300</v>
+      </c>
+      <c r="E59" s="3">
         <v>201400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>175200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>195300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>203700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>243600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>128400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>162700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>158100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>187800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>139200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>133800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>110300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>141400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>96900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>70800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>59100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>71300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>53400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>54500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>50600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>75000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>62100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>52100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>51900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>64500</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>298800</v>
+      </c>
+      <c r="E60" s="3">
         <v>398400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>360800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>344900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>329800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>409000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>275600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>391400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>350100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>403700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>329900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>304000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>253000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>287800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>219600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>131200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>150600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>170300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>201100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>198200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>172500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>187300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>186000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>172600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>150600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>151900</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E61" s="3">
         <v>78600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>79500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>81100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>65700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>71700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>77800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>83600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>89600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>95700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>101700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>107800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>105500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>111000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>215800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>270800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>326300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>281700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>252700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>263300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>273800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>284400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>340700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>380800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>418000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>428600</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>96800</v>
+      </c>
+      <c r="E62" s="3">
         <v>96600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>76700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>72200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>68400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>69500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>79200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>80500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>83500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>79100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>74300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>68100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>53400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>49900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>54600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>56400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>58300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>55500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>15100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>14000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>13500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>13000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>13800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>12600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>12100</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5350,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5442,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5534,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>472900</v>
+      </c>
+      <c r="E66" s="3">
         <v>573600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>517100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>498200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>464000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>550300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>432600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>555500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>523200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>578500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>505900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>479900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>412000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>448600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>489900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>458400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>535100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>507500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>471800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>476500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>460300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>485200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>539800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>567200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>581200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>592700</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5662,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5752,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5844,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +5936,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,97 +6028,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>454300</v>
+      </c>
+      <c r="E72" s="3">
         <v>438400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>359800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>317200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>279100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>268600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>296300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>250800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>204500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>178900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>106000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>53000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-33700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-96100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-147600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-181100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-189500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-194300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-215500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-237600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-240100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-265100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-281800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-300000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-296200</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6212,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6304,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6396,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>646900</v>
+      </c>
+      <c r="E76" s="3">
         <v>723600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>638800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>587200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>542600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>526500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>550700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>499900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>446400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>517800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>439600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>384100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>321300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>288400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>222600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>169000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>131600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>122000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>87900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>64000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>35500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>29000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-37200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-56800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-79000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-76200</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6580,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44562</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44198</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43827</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43463</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43099</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E81" s="3">
         <v>78600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>42700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>38100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-27700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>45500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>46300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>25700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>72900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>53000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>56200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>30500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>62400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>51400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>33500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>21300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>22200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>25200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>17000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>18800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>11300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,55 +6805,56 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E83" s="3">
         <v>12000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>7700</v>
       </c>
       <c r="S83" s="3">
         <v>7700</v>
@@ -6664,40 +6863,43 @@
         <v>7700</v>
       </c>
       <c r="U83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="V83" s="3">
         <v>7400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>6500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>6600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>6200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>5700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>4600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6987,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7079,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7171,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7263,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7355,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-103700</v>
+      </c>
+      <c r="E89" s="3">
         <v>171200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>86000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>75500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-46700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>173100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-88600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>73300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>51000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>62500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-40300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>127300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>166700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>68500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>60300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>16800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>39800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-30000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>57200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>35200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>58300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>25300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>72200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>65600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>21600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-16100</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,97 +7483,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7500</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-8400</v>
       </c>
       <c r="W91" s="3">
         <v>-8400</v>
       </c>
       <c r="X91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7665,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +7757,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-26300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-18100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-19800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +7885,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7709,11 +7943,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-600</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -7741,8 +7975,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8067,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8159,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,163 +8251,169 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-102800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-107600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-102800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-53500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-52600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>45700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-12900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-11100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-10600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-11100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-21500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-45100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-37900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>18300</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>2700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
@@ -8175,104 +8424,110 @@
         <v>0</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E102" s="3">
         <v>157600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>58200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>55300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-66900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>157000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-211900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>52900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>25500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>43500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-63000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>18500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>107300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>45700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>38000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>19000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-61000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>28000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-19200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>10900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>18900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>19400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-9700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>YETI</t>
   </si>
@@ -656,417 +656,430 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44562</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44198</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43099</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>463500</v>
+      </c>
+      <c r="E8" s="3">
         <v>341400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>519800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>433600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>402600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>302800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>448000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>433600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>420000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>293600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>443100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>362600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>357700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>247600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>375800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>294600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>246900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>174400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>297600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>229100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>231700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>155400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>241200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>196100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>206300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>135300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>202100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>183000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>148400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>199200</v>
+      </c>
+      <c r="E9" s="3">
         <v>146600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>204600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>182300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>187700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>140900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>281000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>211100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>200900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>138800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>188300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>155600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>148600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>102400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>150900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>120600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>109400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>82000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>135300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>109000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>115400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>78700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>113400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>98600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>105700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>78100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>109000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>100800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>75400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>264300</v>
+      </c>
+      <c r="E10" s="3">
         <v>194800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>315200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>251300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>214900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>161900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>167000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>222500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>219100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>154800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>254800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>207000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>209200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>145200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>224900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>174000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>137500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>92400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>162300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>120100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>116300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>76700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>127800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>97500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>100600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>57200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>93100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>82200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>73000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1099,8 +1112,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1191,8 +1205,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1283,8 +1300,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1375,8 +1395,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1467,8 +1490,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1524,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>396100</v>
+      </c>
+      <c r="E17" s="3">
         <v>315600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>421600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>371700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>352200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>287700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>491700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>365100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>351700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>260300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>349400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>293900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>285200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>207500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>294300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>224500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>200400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>158300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>285600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>195100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>196700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>146600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>203600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>168000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>173100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>132000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>178200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>158300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>130700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>67400</v>
+      </c>
+      <c r="E18" s="3">
         <v>25800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>98200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>61900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>50400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-43700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>68500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>68300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>33300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>93700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>68700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>72500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>40100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>81500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>70100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>46500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>16200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>34000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>35000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>37600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>28100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>33200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>23900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>24700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>17700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,221 +1749,228 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>6500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-100</v>
       </c>
       <c r="AB20" s="3">
         <v>-100</v>
       </c>
       <c r="AC20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E21" s="3">
         <v>33800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>115100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>69000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>63400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>26500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-25900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>71200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>72400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>42800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>101700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>76000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>78900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>47300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>90300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>77500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>55100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>22000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>19200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>41100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>42300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>15400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>43200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>34200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>39300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>8900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>28900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>30600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>23500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>500</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>800</v>
       </c>
       <c r="M22" s="3">
         <v>800</v>
@@ -1942,242 +1982,251 @@
         <v>800</v>
       </c>
       <c r="P22" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q22" s="3">
         <v>900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>6100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>6800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>8100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>8600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E23" s="3">
         <v>22400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>103000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>57600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>50800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-38500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>59700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>61600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>92200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>66700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>70600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>38900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>81100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>68100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>44800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>11200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>28400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>29400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>29900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>20200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>24500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>14700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>16500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>10900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E24" s="3">
         <v>6500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>24400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-10800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>19300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>13700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>18800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>16600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
-      </c>
-      <c r="V24" s="3">
-        <v>7100</v>
       </c>
       <c r="W24" s="3">
         <v>7100</v>
       </c>
       <c r="X24" s="3">
+        <v>7100</v>
+      </c>
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,192 +2317,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E26" s="3">
         <v>15900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>78600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>42700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>38100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-27700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>45500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>46300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>25700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>72900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>53000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>56200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>30500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>62400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>51400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>33500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>21300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>22200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>25200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>17000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>18800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>9700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>11300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>7100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E27" s="3">
         <v>15900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>78600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>42700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>38100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-27700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>45500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>46300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>25700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>72900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>53000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>56200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>30500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>62400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>51400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>33500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>21300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>22200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>25200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>17000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>18800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>9700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>11300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2544,8 +2602,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2606,17 +2667,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2624,20 +2685,23 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2792,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,192 +2887,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>3400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-6500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>100</v>
       </c>
       <c r="AB32" s="3">
         <v>100</v>
       </c>
       <c r="AC32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD32" s="3">
         <v>600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E33" s="3">
         <v>15900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>78600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>42700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>38100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-27700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>45500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>46300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>25700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>72900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>53000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>56200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>30500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>62400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>51400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>33500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>21300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>22200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>25200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>17000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>18800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>11300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,197 +3172,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E35" s="3">
         <v>15900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>78600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>42700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>38100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-27700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>45500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>46300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>25700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>72900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>53000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>56200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>30500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>62400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>51400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>33500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>21300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>22200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>25200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>17000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>18800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>11300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44562</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44198</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43099</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3404,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,100 +3439,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>212900</v>
+      </c>
+      <c r="E41" s="3">
         <v>173900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>439000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>281400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>223100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>167800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>234700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>77800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>92000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>312200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>259300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>233800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>190300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>253300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>234800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>127500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>118200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>72500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>34600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>38000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>19000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>80100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>52100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>71300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>60400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>53700</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3537,192 +3627,201 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>159100</v>
+      </c>
+      <c r="E43" s="3">
         <v>108400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>95800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>127900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>131600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>95600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>79400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>93900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>94300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>83000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>109500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>83300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>81900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>67100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>65400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>71200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>85900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>60200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>82700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>74800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>75900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>63000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>59300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>61900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>65400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>60400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>67200</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>378300</v>
+      </c>
+      <c r="E44" s="3">
         <v>363900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>337200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>341300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>322000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>347000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>371400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>439400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>490000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>413000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>318900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>266000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>221700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>183900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>140100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>134600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>138800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>202400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>185700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>209200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>181400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>164300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>145400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>157700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>149400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>158500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>175100</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3730,183 +3829,189 @@
         <v>57000</v>
       </c>
       <c r="E45" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F45" s="3">
         <v>42500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>40700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>45200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>44500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>40800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>39600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>29600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>24500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>19900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>19600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>13300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>17800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>20100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>13000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>11100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>10500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7100</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>807200</v>
+      </c>
+      <c r="E46" s="3">
         <v>703200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>914400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>791300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>721900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>654900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>718900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>644700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>717000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>635900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>770200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>632200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>561200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>465700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>476500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>454700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>367400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>400600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>360500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>331800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>313000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>266400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>297000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>284600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>297300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>289900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>303000</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3997,192 +4102,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>212300</v>
+      </c>
+      <c r="E48" s="3">
         <v>207100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>208300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>192600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>189500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>179300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>180000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>183700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>183800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>179700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>174000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>163000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>153700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>119100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>112200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>110000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>112300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>116300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>120400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>81200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>80000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>78200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>74100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>72400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>71100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>71500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>73800</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>209800</v>
+      </c>
+      <c r="E49" s="3">
         <v>206800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>171900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>168400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>165200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>155100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>153700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>152400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>152100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>151400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>149600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>148400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>147200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>146500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>146400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>145900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>145800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>145700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>145100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>145000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>144700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>144300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>134300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>135400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>133700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>130300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>128600</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4387,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,100 +4482,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>24100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>2500</v>
       </c>
       <c r="L52" s="3">
         <v>2500</v>
       </c>
       <c r="M52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N52" s="3">
         <v>2600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>2000</v>
       </c>
       <c r="R52" s="3">
         <v>2000</v>
       </c>
       <c r="S52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T52" s="3">
         <v>1900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11000</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,100 +4672,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1232300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1119800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1297200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1155900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1085400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1006500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1076800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>983200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1055400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>969500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1096400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>945500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>864000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>733300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>737100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>712600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>627500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>666800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>629500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>559700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>540400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>495800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>514200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>502600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>510400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>502200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>516400</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4804,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,126 +4839,130 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>175200</v>
+      </c>
+      <c r="E57" s="3">
         <v>139100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>190400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>179100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>143400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>101700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>140800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>122800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>204100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>167400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>191300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>166100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>145700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>120000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>123600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>101900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>41400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>74400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>83800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>105500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>101500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>78200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>68700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>76900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>73500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>51600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>40300</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E58" s="3">
         <v>6400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>24600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>24400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>24600</v>
       </c>
       <c r="L58" s="3">
         <v>24600</v>
@@ -4837,43 +4971,43 @@
         <v>24600</v>
       </c>
       <c r="N58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="O58" s="3">
         <v>24500</v>
       </c>
       <c r="P58" s="3">
-        <v>22700</v>
+        <v>24500</v>
       </c>
       <c r="Q58" s="3">
         <v>22700</v>
       </c>
       <c r="R58" s="3">
+        <v>22700</v>
+      </c>
+      <c r="S58" s="3">
         <v>20800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>18900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>17100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>15200</v>
-      </c>
-      <c r="V58" s="3">
-        <v>42100</v>
       </c>
       <c r="W58" s="3">
         <v>42100</v>
       </c>
       <c r="X58" s="3">
-        <v>43600</v>
+        <v>42100</v>
       </c>
       <c r="Y58" s="3">
         <v>43600</v>
       </c>
       <c r="Z58" s="3">
-        <v>47100</v>
+        <v>43600</v>
       </c>
       <c r="AA58" s="3">
         <v>47100</v>
@@ -4884,8 +5018,8 @@
       <c r="AC58" s="3">
         <v>47100</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
+      <c r="AD58" s="3">
+        <v>47100</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>8</v>
@@ -4893,376 +5027,391 @@
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E59" s="3">
         <v>153300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>201400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>175200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>195300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>203700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>243600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>128400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>162700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>158100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>187800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>139200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>133800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>110300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>141400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>96900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>70800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>59100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>71300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>53400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>54500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>50600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>75000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>62100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>52100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>51900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>64500</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>351900</v>
+      </c>
+      <c r="E60" s="3">
         <v>298800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>398400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>360800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>344900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>329800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>409000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>275600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>391400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>350100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>403700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>329900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>304000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>253000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>287800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>219600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>131200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>150600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>170300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>201100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>198200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>172500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>187300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>186000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>172600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>150600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>151900</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E61" s="3">
         <v>77400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>78600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>79500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>81100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>65700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>71700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>77800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>83600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>89600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>95700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>101700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>107800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>105500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>111000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>215800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>270800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>326300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>281700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>252700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>263300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>273800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>284400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>340700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>380800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>418000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>428600</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>98800</v>
+      </c>
+      <c r="E62" s="3">
         <v>96800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>96600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>76700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>72200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>68400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>69500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>79200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>80500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>83500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>79100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>74300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>68100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>53400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>49900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>54600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>56400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>58300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>55500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>18000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>15100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>14000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>13500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>13000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>13800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>12600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>12100</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5502,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +5597,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,100 +5692,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>526400</v>
+      </c>
+      <c r="E66" s="3">
         <v>472900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>573600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>517100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>498200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>464000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>550300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>432600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>555500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>523200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>578500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>505900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>479900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>412000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>448600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>489900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>458400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>535100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>507500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>471800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>476500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>460300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>485200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>539800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>567200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>581200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>592700</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5824,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +5917,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6012,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5939,8 +6107,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,100 +6202,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>504700</v>
+      </c>
+      <c r="E72" s="3">
         <v>454300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>438400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>359800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>317200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>279100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>268600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>296300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>250800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>204500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>178900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>106000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>53000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-33700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-96100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-147600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-181100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-189500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-194300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-215500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-237600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-240100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-265100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-281800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-300000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-296200</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6392,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6487,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,100 +6582,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>705900</v>
+      </c>
+      <c r="E76" s="3">
         <v>646900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>723600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>638800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>587200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>542600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>526500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>550700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>499900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>446400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>517800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>439600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>384100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>321300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>288400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>222600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>169000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>131600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>122000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>87900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>64000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>35500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>29000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-37200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-56800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-79000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-76200</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,197 +6772,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44562</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44198</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43099</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E81" s="3">
         <v>15900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>78600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>42700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>38100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-27700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>45500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>46300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>25700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>72900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>53000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>56200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>30500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>62400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>51400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>33500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>21300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>22200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>25200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>17000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>18800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>11300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,58 +7004,59 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E83" s="3">
         <v>11500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7500</v>
-      </c>
-      <c r="S83" s="3">
-        <v>7700</v>
       </c>
       <c r="T83" s="3">
         <v>7700</v>
@@ -6866,40 +7065,43 @@
         <v>7700</v>
       </c>
       <c r="V83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="W83" s="3">
         <v>7400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>7300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>6500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>6300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>6200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>4600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7192,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7287,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7382,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7477,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,100 +7572,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-103700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>171200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>86000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>75500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-46700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>173100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-88600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>73300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>51000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>62500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-40300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>127300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>166700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>68500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>60300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>16800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>39800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-30000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>57200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>35200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>58300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>25300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>72200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>65600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>21600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-16100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,100 +7704,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7500</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-8400</v>
       </c>
       <c r="X91" s="3">
         <v>-8400</v>
       </c>
       <c r="Y91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +7892,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,100 +7987,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-58000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-19800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-6200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8119,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7946,11 +8180,11 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-600</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -7978,8 +8212,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8307,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8402,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,169 +8497,175 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-102800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-107600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-102800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-53500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-52600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>45700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-12900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-11100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-10600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-21500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-45100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-37900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>18300</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
@@ -8427,107 +8676,113 @@
         <v>0</v>
       </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-265000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>157600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>58200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>55300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-66900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>157000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-211900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>52900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>25500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>43500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-63000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>18500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>107300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>45700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>38000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>19000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>28000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>10900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>18900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>19400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-9700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>YETI</t>
   </si>
@@ -656,430 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44562</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44198</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43827</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43463</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43372</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43099</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42917</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>478400</v>
+      </c>
+      <c r="E8" s="3">
         <v>463500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>341400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>519800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>433600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>402600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>302800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>448000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>433600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>420000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>293600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>443100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>362600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>357700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>247600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>375800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>294600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>246900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>174400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>297600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>229100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>231700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>155400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>241200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>196100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>206300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>135300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>202100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>183000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>148400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>200700</v>
+      </c>
+      <c r="E9" s="3">
         <v>199200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>146600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>204600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>182300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>187700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>140900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>281000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>211100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>200900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>138800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>188300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>155600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>148600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>102400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>150900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>120600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>109400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>82000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>135300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>109000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>115400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>78700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>113400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>98600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>105700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>78100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>109000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>100800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>75400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>277700</v>
+      </c>
+      <c r="E10" s="3">
         <v>264300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>194800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>315200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>251300</v>
       </c>
-      <c r="H10" s="3">
-        <v>214900</v>
-      </c>
       <c r="I10" s="3">
+        <v>214800</v>
+      </c>
+      <c r="J10" s="3">
         <v>161900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>167000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>222500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>219100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>154800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>254800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>207000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>209200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>145200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>224900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>174000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>137500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>92400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>162300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>120100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>116300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>76700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>127800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>97500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>100600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>57200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>93100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>82200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>73000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1113,8 +1126,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1127,8 +1141,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>15500</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1208,8 +1222,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1303,31 +1320,34 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1398,31 +1418,34 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>12100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>12100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>11800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>11400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1493,8 +1516,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1525,198 +1551,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>408800</v>
+      </c>
+      <c r="E17" s="3">
         <v>396100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>315600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>421600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>371700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>352200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>287700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>491700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>365100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>351700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>260300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>349400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>293900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>285200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>207500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>294300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>224500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>200400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>158300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>285600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>195100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>196700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>146600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>203600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>168000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>173100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>132000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>178200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>158300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>130700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E18" s="3">
         <v>67400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>25800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>98200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>61900</v>
       </c>
-      <c r="H18" s="3">
-        <v>50400</v>
-      </c>
       <c r="I18" s="3">
+        <v>50300</v>
+      </c>
+      <c r="J18" s="3">
         <v>15100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-43700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>68500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>68300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>33300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>93700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>68700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>72500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>40100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>81500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>70100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>46500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>16200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>34000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>35000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>8800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>37600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>28100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>33200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>23900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>24700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>17700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1750,230 +1783,237 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>400</v>
+        <v>-4100</v>
       </c>
       <c r="E20" s="3">
-        <v>-3400</v>
+        <v>-400</v>
       </c>
       <c r="F20" s="3">
-        <v>4900</v>
+        <v>4100</v>
       </c>
       <c r="G20" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="H20" s="3">
-        <v>1200</v>
+        <v>4000</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>6500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-100</v>
       </c>
       <c r="AC20" s="3">
         <v>-100</v>
       </c>
       <c r="AD20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E21" s="3">
         <v>79900</v>
       </c>
-      <c r="E21" s="3">
-        <v>33800</v>
-      </c>
       <c r="F21" s="3">
-        <v>115100</v>
+        <v>33200</v>
       </c>
       <c r="G21" s="3">
+        <v>114400</v>
+      </c>
+      <c r="H21" s="3">
         <v>69000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>63400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-25900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>71200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>72400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>42800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>101700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>76000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>78900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>47300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>90300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>77500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>55100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>22000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>19200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>41100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>42300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>15400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>43200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>34200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>39300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>28900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>30600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>23500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
         <v>500</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G22" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>800</v>
       </c>
       <c r="N22" s="3">
         <v>800</v>
@@ -1985,248 +2025,257 @@
         <v>800</v>
       </c>
       <c r="Q22" s="3">
+        <v>800</v>
+      </c>
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>6100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>6800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>7800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>8600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>8100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E23" s="3">
         <v>67300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>103000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>57600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>50800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>14500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-38500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>59700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>61600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>33400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>92200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>66700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>70600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>38900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>81100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>68100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>44800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>11200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>28400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>29400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>29900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>20200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>24500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>14700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>16500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>10900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E24" s="3">
         <v>16900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>24400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-10800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>13700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>18800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>16600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>11300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2000</v>
-      </c>
-      <c r="W24" s="3">
-        <v>7100</v>
       </c>
       <c r="X24" s="3">
         <v>7100</v>
       </c>
       <c r="Y24" s="3">
+        <v>7100</v>
+      </c>
+      <c r="Z24" s="3">
         <v>600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2320,198 +2369,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E26" s="3">
         <v>50400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>78600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>42700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>38100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-27700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>45500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>46300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>25700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>72900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>53000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>56200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>30500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>62400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>51400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>33500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>21300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>22200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>25200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>17000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>18800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>9700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>11300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>7100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E27" s="3">
         <v>50400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>78600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>42700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>38100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-27700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>45500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>46300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>25700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>72900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>53000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>56200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>30500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>62400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>51400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>33500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>21300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>22200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>25200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>17000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>18800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>9700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>11300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>7000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2605,8 +2663,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2670,17 +2731,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2688,20 +2749,23 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2795,8 +2859,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2890,198 +2957,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-400</v>
+        <v>4100</v>
       </c>
       <c r="E32" s="3">
-        <v>3400</v>
+        <v>400</v>
       </c>
       <c r="F32" s="3">
-        <v>-4900</v>
+        <v>-4100</v>
       </c>
       <c r="G32" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="H32" s="3">
-        <v>-1200</v>
+        <v>-4000</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-6500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>300</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>100</v>
       </c>
       <c r="AC32" s="3">
         <v>100</v>
       </c>
       <c r="AD32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE32" s="3">
         <v>600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E33" s="3">
         <v>50400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>78600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>42700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>38100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-27700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>45500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>46300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>25700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>72900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>53000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>56200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>30500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>62400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>51400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>33500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>21300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>22200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>25200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>17000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>18800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>11300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>7000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3175,203 +3251,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E35" s="3">
         <v>50400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>78600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>42700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>38100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-27700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>45500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>46300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>25700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>72900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>53000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>56200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>30500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>62400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>51400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>33500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>21300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>22200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>25200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>17000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>18800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>11300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>7000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44562</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44198</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43827</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43463</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43372</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43099</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42917</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3405,8 +3490,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3440,103 +3526,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>280500</v>
+      </c>
+      <c r="E41" s="3">
         <v>212900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>173900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>439000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>281400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>223100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>167800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>234700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>77800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>92000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>312200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>259300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>233800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>190300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>253300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>234800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>127500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>118200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>72500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>34600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>38000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>19000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>80100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>52100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>71300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>60400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>53700</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3630,411 +3720,426 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>143700</v>
+      </c>
+      <c r="E43" s="3">
         <v>159100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>108400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>95800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>127900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>131600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>95600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>79400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>93900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>94300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>83000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>109500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>83300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>81900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>67100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>65400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>71200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>85900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>60200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>82700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>74800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>75900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>63000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>59300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>61900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>65400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>60400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>67200</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>370200</v>
+      </c>
+      <c r="E44" s="3">
         <v>378300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>363900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>337200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>341300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>322000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>347000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>371400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>439400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>490000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>413000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>318900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>266000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>221700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>183900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>140100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>134600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>138800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>202400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>185700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>209200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>181400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>164300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>145400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>157700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>149400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>158500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>175100</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>57000</v>
+        <v>7900</v>
       </c>
       <c r="E45" s="3">
-        <v>57000</v>
+        <v>8400</v>
       </c>
       <c r="F45" s="3">
-        <v>42500</v>
+        <v>7900</v>
       </c>
       <c r="G45" s="3">
-        <v>40700</v>
+        <v>6200</v>
       </c>
       <c r="H45" s="3">
-        <v>45200</v>
+        <v>5200</v>
       </c>
       <c r="I45" s="3">
-        <v>44500</v>
+        <v>3900</v>
       </c>
       <c r="J45" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K45" s="3">
         <v>33300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>40800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>39600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>29600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>24500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>19900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>19600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>13300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>17800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>20100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>12200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>13000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>11100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>10500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7100</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>846300</v>
+      </c>
+      <c r="E46" s="3">
         <v>807200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>703200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>914400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>791300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>721900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>654900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>718900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>644700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>717000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>635900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>770200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>632200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>561200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>465700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>476500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>454700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>367400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>400600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>360500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>331800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>313000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>266400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>297000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>284600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>297300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>289900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>303000</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4105,198 +4210,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>213000</v>
+      </c>
+      <c r="E48" s="3">
         <v>212300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>207100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>208300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>192600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>189500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>179300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>180000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>183700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>183800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>179700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>174000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>163000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>153700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>119100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>112200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>110000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>112300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>116300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>120400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>81200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>80000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>78200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>74100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>72400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>71100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>71500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>73800</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>210800</v>
+      </c>
+      <c r="E49" s="3">
         <v>209800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>206800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>171900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>168400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>165200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>155100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>153700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>152400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>152100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>151400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>149600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>148400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>147200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>146500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>146400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>145900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>145800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>145700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>145100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>145000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>144700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>144300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>134300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>135400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>133700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>130300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>128600</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4390,8 +4504,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4485,8 +4602,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4494,94 +4614,97 @@
         <v>3000</v>
       </c>
       <c r="E52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F52" s="3">
         <v>2700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2600</v>
       </c>
-      <c r="G52" s="3">
-        <v>3500</v>
-      </c>
       <c r="H52" s="3">
-        <v>8800</v>
+        <v>900</v>
       </c>
       <c r="I52" s="3">
+        <v>900</v>
+      </c>
+      <c r="J52" s="3">
         <v>17300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2400</v>
-      </c>
-      <c r="L52" s="3">
-        <v>2500</v>
       </c>
       <c r="M52" s="3">
         <v>2500</v>
       </c>
       <c r="N52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O52" s="3">
         <v>2600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1900</v>
-      </c>
-      <c r="R52" s="3">
-        <v>2000</v>
       </c>
       <c r="S52" s="3">
         <v>2000</v>
       </c>
       <c r="T52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U52" s="3">
         <v>1900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>11000</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4675,103 +4798,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1273200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1232300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1119800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1297200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1155900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1085400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1006500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1076800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>983200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1055400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>969500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1096400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>945500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>864000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>733300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>737100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>712600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>627500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>666800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>629500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>559700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>540400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>495800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>514200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>502600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>510400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>502200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>516400</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4805,8 +4934,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4840,132 +4970,136 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>148200</v>
+      </c>
+      <c r="E57" s="3">
         <v>175200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>139100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>190400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>179100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>143400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>101700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>140800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>122800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>204100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>167400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>191300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>166100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>145700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>120000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>123600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>101900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>41400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>74400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>83800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>105500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>101500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>78200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>68700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>76900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>73500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>51600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>40300</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6500</v>
+        <v>23700</v>
       </c>
       <c r="E58" s="3">
-        <v>6400</v>
+        <v>22800</v>
       </c>
       <c r="F58" s="3">
-        <v>6600</v>
+        <v>22100</v>
       </c>
       <c r="G58" s="3">
-        <v>6500</v>
+        <v>21300</v>
       </c>
       <c r="H58" s="3">
-        <v>6200</v>
+        <v>19900</v>
       </c>
       <c r="I58" s="3">
+        <v>17900</v>
+      </c>
+      <c r="J58" s="3">
+        <v>35700</v>
+      </c>
+      <c r="K58" s="3">
+        <v>24600</v>
+      </c>
+      <c r="L58" s="3">
         <v>24400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>24600</v>
-      </c>
-      <c r="K58" s="3">
-        <v>24400</v>
-      </c>
-      <c r="L58" s="3">
-        <v>24600</v>
       </c>
       <c r="M58" s="3">
         <v>24600</v>
@@ -4974,43 +5108,43 @@
         <v>24600</v>
       </c>
       <c r="O58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="P58" s="3">
         <v>24500</v>
       </c>
       <c r="Q58" s="3">
-        <v>22700</v>
+        <v>24500</v>
       </c>
       <c r="R58" s="3">
         <v>22700</v>
       </c>
       <c r="S58" s="3">
+        <v>22700</v>
+      </c>
+      <c r="T58" s="3">
         <v>20800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>18900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>17100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>15200</v>
-      </c>
-      <c r="W58" s="3">
-        <v>42100</v>
       </c>
       <c r="X58" s="3">
         <v>42100</v>
       </c>
       <c r="Y58" s="3">
-        <v>43600</v>
+        <v>42100</v>
       </c>
       <c r="Z58" s="3">
         <v>43600</v>
       </c>
       <c r="AA58" s="3">
-        <v>47100</v>
+        <v>43600</v>
       </c>
       <c r="AB58" s="3">
         <v>47100</v>
@@ -5021,8 +5155,8 @@
       <c r="AD58" s="3">
         <v>47100</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
+      <c r="AE58" s="3">
+        <v>47100</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
@@ -5030,388 +5164,403 @@
       <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>170200</v>
+        <v>73700</v>
       </c>
       <c r="E59" s="3">
-        <v>153300</v>
+        <v>73500</v>
       </c>
       <c r="F59" s="3">
-        <v>201400</v>
+        <v>79800</v>
       </c>
       <c r="G59" s="3">
-        <v>175200</v>
+        <v>96700</v>
       </c>
       <c r="H59" s="3">
-        <v>195300</v>
+        <v>83100</v>
       </c>
       <c r="I59" s="3">
-        <v>203700</v>
+        <v>118200</v>
       </c>
       <c r="J59" s="3">
+        <v>92900</v>
+      </c>
+      <c r="K59" s="3">
         <v>243600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>128400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>162700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>158100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>187800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>139200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>133800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>110300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>141400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>96900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>70800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>59100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>71300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>53400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>54500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>50600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>75000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>62100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>52100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>51900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>64500</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>328100</v>
+      </c>
+      <c r="E60" s="3">
         <v>351900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>298800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>398400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>360800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>344900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>329800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>409000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>275600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>391400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>350100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>403700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>329900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>304000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>253000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>287800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>219600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>131200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>150600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>170300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>201100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>198200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>172500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>187300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>186000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>172600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>150600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>151900</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>75800</v>
+        <v>154300</v>
       </c>
       <c r="E61" s="3">
-        <v>77400</v>
+        <v>154000</v>
       </c>
       <c r="F61" s="3">
-        <v>78600</v>
+        <v>152800</v>
       </c>
       <c r="G61" s="3">
-        <v>79500</v>
+        <v>154800</v>
       </c>
       <c r="H61" s="3">
-        <v>81100</v>
+        <v>139700</v>
       </c>
       <c r="I61" s="3">
-        <v>65700</v>
+        <v>138400</v>
       </c>
       <c r="J61" s="3">
+        <v>119900</v>
+      </c>
+      <c r="K61" s="3">
         <v>71700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>77800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>83600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>89600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>95700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>101700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>107800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>105500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>111000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>215800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>270800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>326300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>281700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>252700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>263300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>273800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>284400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>340700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>380800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>418000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>428600</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>98800</v>
+        <v>19500</v>
       </c>
       <c r="E62" s="3">
-        <v>96800</v>
+        <v>18300</v>
       </c>
       <c r="F62" s="3">
-        <v>96600</v>
+        <v>17200</v>
       </c>
       <c r="G62" s="3">
-        <v>76700</v>
+        <v>20400</v>
       </c>
       <c r="H62" s="3">
-        <v>72200</v>
+        <v>16500</v>
       </c>
       <c r="I62" s="3">
-        <v>68400</v>
+        <v>14900</v>
       </c>
       <c r="J62" s="3">
+        <v>14200</v>
+      </c>
+      <c r="K62" s="3">
         <v>69500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>79200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>80500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>83500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>79100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>74300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>68100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>53400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>49900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>54600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>56400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>58300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>55500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>18000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>15100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>14000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>13500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>13000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>13800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>12600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>12100</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5505,8 +5654,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5600,8 +5752,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5695,103 +5850,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>503200</v>
+      </c>
+      <c r="E66" s="3">
         <v>526400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>472900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>573600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>517100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>498200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>464000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>550300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>432600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>555500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>523200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>578500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>505900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>479900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>412000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>448600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>489900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>458400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>535100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>507500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>471800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>476500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>460300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>485200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>539800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>567200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>581200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>592700</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5825,8 +5986,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5920,8 +6082,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6015,8 +6180,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6110,8 +6278,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6205,103 +6376,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>561000</v>
+      </c>
+      <c r="E72" s="3">
         <v>504700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>454300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>438400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>359800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>317200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>279100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>268600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>296300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>250800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>204500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>178900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>106000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>53000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-33700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-96100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-147600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-181100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-189500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-194300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-215500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-237600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-240100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-265100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-281800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-300000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-296200</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6395,8 +6572,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6490,8 +6670,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6585,103 +6768,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>770000</v>
+      </c>
+      <c r="E76" s="3">
         <v>705900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>646900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>723600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>638800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>587200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>542600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>526500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>550700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>499900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>446400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>517800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>439600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>384100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>321300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>288400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>222600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>169000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>131600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>122000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>87900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>64000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>35500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>29000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-37200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-56800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-79000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-76200</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6775,203 +6964,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44562</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44198</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43827</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43463</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43372</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43099</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42917</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E81" s="3">
         <v>50400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>78600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>42700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>38100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-27700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>45500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>46300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>25700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>72900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>53000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>56200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>30500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>62400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>51400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>33500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>21300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>22200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>25200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>17000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>18800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>11300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>7000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7005,61 +7203,62 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12100</v>
+        <v>11200</v>
       </c>
       <c r="E83" s="3">
-        <v>11500</v>
+        <v>11800</v>
       </c>
       <c r="F83" s="3">
-        <v>12000</v>
+        <v>11400</v>
       </c>
       <c r="G83" s="3">
-        <v>11200</v>
+        <v>4400</v>
       </c>
       <c r="H83" s="3">
-        <v>11800</v>
+        <v>10000</v>
       </c>
       <c r="I83" s="3">
-        <v>11400</v>
+        <v>9800</v>
       </c>
       <c r="J83" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K83" s="3">
         <v>11300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7500</v>
-      </c>
-      <c r="T83" s="3">
-        <v>7700</v>
       </c>
       <c r="U83" s="3">
         <v>7700</v>
@@ -7068,40 +7267,43 @@
         <v>7700</v>
       </c>
       <c r="W83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="X83" s="3">
         <v>7400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>7300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>6600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>6300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>6200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>4600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7195,8 +7397,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7290,8 +7495,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7385,8 +7593,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7480,8 +7691,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7575,103 +7789,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>83500</v>
+      </c>
+      <c r="E89" s="3">
         <v>56000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-103700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>171200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>86000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>75500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-46700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>173100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-88600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>73300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>51000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>62500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-40300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>127300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>166700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>68500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>60300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>16800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>39800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-30000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>57200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>35200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>58300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>25300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>72200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>65600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>21600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-16100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7705,103 +7925,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7500</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-8400</v>
       </c>
       <c r="Y91" s="3">
         <v>-8400</v>
       </c>
       <c r="Z91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7895,8 +8119,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7990,103 +8217,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-58000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-26300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-18100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-19800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-9500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-6200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8120,31 +8353,32 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8183,11 +8417,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-600</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -8215,8 +8449,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8310,8 +8547,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8405,8 +8645,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8500,289 +8743,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-102800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-107600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-102800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-53500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-52600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>45700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-12900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-11100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-10600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-21500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-45100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-37900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>18300</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F101" s="3">
+        <v>400</v>
+      </c>
+      <c r="G101" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J101" s="3">
+        <v>400</v>
+      </c>
+      <c r="K101" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N101" s="3">
+        <v>400</v>
+      </c>
+      <c r="O101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="F101" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="S101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="T101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="M101" s="3">
-        <v>400</v>
-      </c>
-      <c r="N101" s="3">
-        <v>2200</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="R101" s="3">
-        <v>600</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="T101" s="3">
-        <v>400</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E102" s="3">
         <v>39000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-265000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>157600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>58200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>55300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-66900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>157000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-211900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>52900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>43500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-63000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>18500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>107300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>45700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>38000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>19000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-61000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>28000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>10900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>18900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>19400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-9700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
   <si>
     <t>YETI</t>
   </si>
@@ -656,443 +656,455 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44562</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44380</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44289</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44198</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44009</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43827</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43736</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43554</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43463</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43372</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43099</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42917</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>546500</v>
+      </c>
+      <c r="E8" s="3">
         <v>478400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>463500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>341400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>519800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>433600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>402600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>302800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>448000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>433600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>420000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>293600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>443100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>362600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>357700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>247600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>375800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>294600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>246900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>174400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>297600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>229100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>231700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>155400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>241200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>196100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>206300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>135300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>202100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>183000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>148400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>220100</v>
+      </c>
+      <c r="E9" s="3">
         <v>200700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>199200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>146600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>204600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>182300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>187700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>140900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>281000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>211100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>200900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>138800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>188300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>155600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>148600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>102400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>150900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>120600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>109400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>82000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>135300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>109000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>115400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>78700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>113400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>98600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>105700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>78100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>109000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>100800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>75400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>326400</v>
+      </c>
+      <c r="E10" s="3">
         <v>277700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>264300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>194800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>315200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>251300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>214800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>161900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>167000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>222500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>219100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>154800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>254800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>207000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>209200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>145200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>224900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>174000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>137500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>92400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>162300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>120100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>116300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>76700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>127800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>97500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>100600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>57200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>93100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>82200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>73000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,13 +1139,14 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>21100</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1141,12 +1154,12 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>15500</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1225,8 +1238,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1323,8 +1339,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1349,8 +1368,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1421,35 +1440,38 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>12100</v>
+        <v>29200</v>
       </c>
       <c r="E15" s="3">
         <v>12100</v>
       </c>
       <c r="F15" s="3">
+        <v>12100</v>
+      </c>
+      <c r="G15" s="3">
         <v>11500</v>
       </c>
-      <c r="G15" s="3">
-        <v>12000</v>
-      </c>
       <c r="H15" s="3">
+        <v>29800</v>
+      </c>
+      <c r="I15" s="3">
         <v>11200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1519,8 +1541,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1552,204 +1577,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>464000</v>
+      </c>
+      <c r="E17" s="3">
         <v>408800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>396100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>315600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>421600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>371700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>352200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>287700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>491700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>365100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>351700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>260300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>349400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>293900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>285200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>207500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>294300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>224500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>200400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>158300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>285600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>195100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>196700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>146600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>203600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>168000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>173100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>132000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>178200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>158300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>130700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E18" s="3">
         <v>69600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>67400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>25800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>98200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>61900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>50300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-43700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>68500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>68300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>33300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>93700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>68700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>72500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>40100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>81500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>70100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>46500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>16200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>34000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>35000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>37600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>28100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>33200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>23900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>24700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>17700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1784,239 +1816,246 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>6500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-100</v>
       </c>
       <c r="AD20" s="3">
         <v>-100</v>
       </c>
       <c r="AE20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>98100</v>
+      </c>
+      <c r="E21" s="3">
         <v>85800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>79900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>33200</v>
       </c>
-      <c r="G21" s="3">
-        <v>114400</v>
-      </c>
       <c r="H21" s="3">
+        <v>132200</v>
+      </c>
+      <c r="I21" s="3">
         <v>69000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>63400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-25900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>71200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>72400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>42800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>101700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>76000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>78900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>47300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>90300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>77500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>55100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>22000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>19200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>41100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>42300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>15400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>43200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>34200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>39300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>8900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>28900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>30600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>23500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3">
         <v>-700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>800</v>
       </c>
       <c r="O22" s="3">
         <v>800</v>
@@ -2028,254 +2067,263 @@
         <v>800</v>
       </c>
       <c r="R22" s="3">
+        <v>800</v>
+      </c>
+      <c r="S22" s="3">
         <v>900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>5700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>6100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>7800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>8600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E23" s="3">
         <v>74100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>67300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>103000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>57600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>50800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-38500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>59700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>61600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>33400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>92200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>66700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>70600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>38900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>81100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>68100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>44800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>11200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>28400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>29400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>29900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>20200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>24500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>14700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>16500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>10900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E24" s="3">
         <v>17800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>24400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-10800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>19300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>18800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>16600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>11300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2000</v>
-      </c>
-      <c r="X24" s="3">
-        <v>7100</v>
       </c>
       <c r="Y24" s="3">
         <v>7100</v>
       </c>
       <c r="Z24" s="3">
+        <v>7100</v>
+      </c>
+      <c r="AA24" s="3">
         <v>600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2372,204 +2420,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E26" s="3">
         <v>56300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>50400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>78600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>42700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>38100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-27700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>45500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>46300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>25700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>72900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>53000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>56200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>30500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>62400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>51400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>33500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>21300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>22200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>25200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>17000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>18800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>9700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>11300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>7100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E27" s="3">
         <v>56300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>50400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>78600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>42700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>38100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-27700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>45500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>46300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>25700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>72900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>53000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>56200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>30500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>62400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>51400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>33500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>21300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>22200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>25200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>17000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>18800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>9700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>11300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>7000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2666,8 +2723,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2734,17 +2794,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2752,20 +2812,23 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2862,8 +2925,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2960,204 +3026,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E32" s="3">
         <v>4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-6500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>200</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>100</v>
       </c>
       <c r="AD32" s="3">
         <v>100</v>
       </c>
       <c r="AE32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF32" s="3">
         <v>600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E33" s="3">
         <v>56300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>50400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>78600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>42700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>38100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-27700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>45500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>46300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>25700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>72900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>53000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>56200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>30500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>62400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>51400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>33500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>21300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>22200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>25200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>17000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>18800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>11300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>7000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3254,209 +3329,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E35" s="3">
         <v>56300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>50400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>78600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>42700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>38100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-27700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>45500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>46300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>25700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>72900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>53000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>56200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>30500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>62400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>51400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>33500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>21300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>22200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>25200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>17000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>18800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>11300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>7000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44562</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44380</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44289</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44198</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44009</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43827</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43736</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43554</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43463</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43372</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43099</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42917</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3491,8 +3575,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3527,106 +3612,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>358800</v>
+      </c>
+      <c r="E41" s="3">
         <v>280500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>212900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>173900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>439000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>281400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>223100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>167800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>234700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>77800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>92000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>100300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>312200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>259300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>233800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>190300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>253300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>234800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>127500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>118200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>72500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>34600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>38000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>19000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>80100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>52100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>71300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>60400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>53700</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH41" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3723,400 +3812,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>120200</v>
+      </c>
+      <c r="E43" s="3">
         <v>143700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>159100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>108400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>95800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>127900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>131600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>95600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>79400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>93900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>94300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>83000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>109500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>83300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>81900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>67100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>65400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>71200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>85900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>60200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>82700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>74800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>75900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>63000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>59300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>61900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>65400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>60400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>67200</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>310100</v>
+      </c>
+      <c r="E44" s="3">
         <v>370200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>378300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>363900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>337200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>341300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>322000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>347000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>371400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>439400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>490000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>413000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>318900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>266000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>221700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>183900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>140100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>134600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>138800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>202400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>185700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>209200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>181400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>164300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>145400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>157700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>149400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>158500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>175100</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH44" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E45" s="3">
         <v>7900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>40800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>39600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>29600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>24500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>14100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>19900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>19600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>13300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>17800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>20100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>12200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>13000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>11100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>10500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7100</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>826800</v>
+      </c>
+      <c r="E46" s="3">
         <v>846300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>807200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>703200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>914400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>791300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>721900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>654900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>718900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>644700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>717000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>635900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>770200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>632200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>561200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>465700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>476500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>454700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>367400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>400600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>360500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>331800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>313000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>266400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>297000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>284600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>297300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>289900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>303000</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH46" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4141,8 +4245,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4213,204 +4317,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>204500</v>
+      </c>
+      <c r="E48" s="3">
         <v>213000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>212300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>207100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>208300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>192600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>189500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>179300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>180000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>183700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>183800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>179700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>174000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>163000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>153700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>119100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>112200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>110000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>112300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>116300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>120400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>81200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>80000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>78200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>74100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>72400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>71100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>71500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>73800</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>244600</v>
+      </c>
+      <c r="E49" s="3">
         <v>210800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>209800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>206800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>171900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>168400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>165200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>155100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>153700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>152400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>152100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>151400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>149600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>148400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>147200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>146500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>146400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>145900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>145800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>145700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>145100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>145000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>144700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>144300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>134300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>135400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>133700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>130300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>128600</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4507,8 +4620,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4605,106 +4721,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3000</v>
+        <v>10200</v>
       </c>
       <c r="E52" s="3">
         <v>3000</v>
       </c>
       <c r="F52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G52" s="3">
         <v>2700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>900</v>
       </c>
       <c r="I52" s="3">
         <v>900</v>
       </c>
       <c r="J52" s="3">
+        <v>900</v>
+      </c>
+      <c r="K52" s="3">
         <v>17300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2400</v>
-      </c>
-      <c r="M52" s="3">
-        <v>2500</v>
       </c>
       <c r="N52" s="3">
         <v>2500</v>
       </c>
       <c r="O52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P52" s="3">
         <v>2600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1900</v>
-      </c>
-      <c r="S52" s="3">
-        <v>2000</v>
       </c>
       <c r="T52" s="3">
         <v>2000</v>
       </c>
       <c r="U52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="V52" s="3">
         <v>1900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11000</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH52" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4801,106 +4923,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1286100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1273200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1232300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1119800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1297200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1155900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1085400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1006500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1076800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>983200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1055400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>969500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1096400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>945500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>864000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>733300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>737100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>712600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>627500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>666800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>629500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>559700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>540400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>495800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>514200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>502600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>510400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>502200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>516400</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH54" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4935,8 +5063,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4971,138 +5100,142 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>158500</v>
+      </c>
+      <c r="E57" s="3">
         <v>148200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>175200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>139100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>190400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>179100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>143400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>101700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>140800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>122800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>204100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>167400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>191300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>166100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>145700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>120000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>123600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>101900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>41400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>74400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>83800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>105500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>101500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>78200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>68700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>76900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>73500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>51600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>40300</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH57" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E58" s="3">
         <v>23700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>22800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>22100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>21300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>35700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>24600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24400</v>
-      </c>
-      <c r="M58" s="3">
-        <v>24600</v>
       </c>
       <c r="N58" s="3">
         <v>24600</v>
@@ -5111,43 +5244,43 @@
         <v>24600</v>
       </c>
       <c r="P58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="Q58" s="3">
         <v>24500</v>
       </c>
       <c r="R58" s="3">
-        <v>22700</v>
+        <v>24500</v>
       </c>
       <c r="S58" s="3">
         <v>22700</v>
       </c>
       <c r="T58" s="3">
+        <v>22700</v>
+      </c>
+      <c r="U58" s="3">
         <v>20800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>18900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>17100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>15200</v>
-      </c>
-      <c r="X58" s="3">
-        <v>42100</v>
       </c>
       <c r="Y58" s="3">
         <v>42100</v>
       </c>
       <c r="Z58" s="3">
-        <v>43600</v>
+        <v>42100</v>
       </c>
       <c r="AA58" s="3">
         <v>43600</v>
       </c>
       <c r="AB58" s="3">
-        <v>47100</v>
+        <v>43600</v>
       </c>
       <c r="AC58" s="3">
         <v>47100</v>
@@ -5158,8 +5291,8 @@
       <c r="AE58" s="3">
         <v>47100</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
+      <c r="AF58" s="3">
+        <v>47100</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
@@ -5167,400 +5300,415 @@
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E59" s="3">
         <v>73700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>73500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>79800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>96700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>83100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>118200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>92900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>243600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>128400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>162700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>158100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>187800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>139200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>133800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>110300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>141400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>96900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>70800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>59100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>71300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>53400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>54500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>50600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>75000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>62100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>52100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>51900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>64500</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>379500</v>
+      </c>
+      <c r="E60" s="3">
         <v>328100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>351900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>298800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>398400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>360800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>344900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>329800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>409000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>275600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>391400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>350100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>403700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>329900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>304000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>253000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>287800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>219600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>131200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>150600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>170300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>201100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>198200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>172500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>187300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>186000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>172600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>150600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>151900</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH60" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>146400</v>
+      </c>
+      <c r="E61" s="3">
         <v>154300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>154000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>152800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>154800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>139700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>138400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>119900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>71700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>77800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>83600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>89600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>95700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>101700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>107800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>105500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>111000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>215800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>270800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>326300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>281700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>252700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>263300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>273800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>284400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>340700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>380800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>418000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>428600</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E62" s="3">
         <v>19500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>17200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>16500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>69500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>79200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>80500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>83500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>79100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>74300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>68100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>53400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>49900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>54600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>56400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>58300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>55500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>18000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>15100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>14000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>13500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>13000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>13800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>12600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>12100</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5657,8 +5805,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5755,8 +5906,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5853,106 +6007,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>546000</v>
+      </c>
+      <c r="E66" s="3">
         <v>503200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>526400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>472900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>573600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>517100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>498200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>464000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>550300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>432600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>555500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>523200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>578500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>505900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>479900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>412000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>448600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>489900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>458400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>535100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>507500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>471800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>476500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>460300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>485200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>539800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>567200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>581200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>592700</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH66" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5987,8 +6147,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6085,8 +6246,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6183,8 +6347,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6281,8 +6448,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6379,106 +6549,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>614100</v>
+      </c>
+      <c r="E72" s="3">
         <v>561000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>504700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>454300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>438400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>359800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>317200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>279100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>268600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>296300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>250800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>204500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>178900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>106000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>53000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-33700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-96100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-147600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-181100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-189500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-194300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-215500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-237600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-240100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-265100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-281800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-300000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-296200</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6575,8 +6751,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6673,8 +6852,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6771,106 +6953,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>740100</v>
+      </c>
+      <c r="E76" s="3">
         <v>770000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>705900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>646900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>723600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>638800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>587200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>542600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>526500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>550700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>499900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>446400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>517800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>439600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>384100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>321300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>288400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>222600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>169000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>131600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>122000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>87900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>64000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>35500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>29000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-37200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-56800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-79000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-76200</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH76" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6967,209 +7155,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44562</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44380</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44289</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44198</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44009</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43827</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43736</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43554</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43463</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43372</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43099</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42917</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E81" s="3">
         <v>56300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>50400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>78600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>42700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>38100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-27700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>45500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>46300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>25700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>72900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>53000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>56200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>30500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>62400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>51400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>33500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>21300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>22200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>25200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>17000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>18800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>11300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>7000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7204,64 +7401,65 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E83" s="3">
         <v>11200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>8700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7500</v>
-      </c>
-      <c r="U83" s="3">
-        <v>7700</v>
       </c>
       <c r="V83" s="3">
         <v>7700</v>
@@ -7270,40 +7468,43 @@
         <v>7700</v>
       </c>
       <c r="X83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="Y83" s="3">
         <v>7400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>7300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>6500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>6600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>6300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>6200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7400,8 +7601,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7498,8 +7702,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7596,8 +7803,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7694,8 +7904,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7792,106 +8005,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>225600</v>
+      </c>
+      <c r="E89" s="3">
         <v>83500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>56000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-103700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>171200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>86000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>75500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-46700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>173100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>14000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-88600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>73300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>51000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>62500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-40300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>127300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>166700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>68500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>60300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>16800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>39800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-30000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>57200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>35200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>58300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>25300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>72200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>65600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>21600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-16100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7926,106 +8145,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7500</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-8400</v>
       </c>
       <c r="Z91" s="3">
         <v>-8400</v>
       </c>
       <c r="AA91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8122,8 +8345,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8220,106 +8446,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-58000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-26300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-17800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-15000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8354,8 +8586,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8380,8 +8613,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8420,11 +8653,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-600</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -8452,8 +8685,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8550,8 +8786,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8648,8 +8887,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8746,181 +8988,187 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-101700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-102800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-107600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-102800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-53500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-52600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>45700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-12900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-10600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-21500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-45100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-37900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>18300</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
@@ -8931,113 +9179,119 @@
         <v>0</v>
       </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E102" s="3">
         <v>67500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>39000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-265000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>157600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>58200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>55300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-66900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>157000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-211900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>52900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>43500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-63000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>18500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>107300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>45700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>38000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>19000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-61000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>28000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>10900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>18900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>19400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-9700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>YETI</t>
   </si>
@@ -656,455 +656,468 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45654</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44562</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44380</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44289</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44198</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44009</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43918</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43827</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43736</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43554</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43463</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43372</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43099</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42917</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>351100</v>
+      </c>
+      <c r="E8" s="3">
         <v>546500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>478400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>463500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>341400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>519800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>433600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>402600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>302800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>448000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>433600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>420000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>293600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>443100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>362600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>357700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>247600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>375800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>294600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>246900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>174400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>297600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>229100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>231700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>155400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>241200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>196100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>206300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>135300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>202100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>183000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>148400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>149400</v>
+      </c>
+      <c r="E9" s="3">
         <v>220100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>200700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>199200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>146600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>204600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>182300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>187700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>140900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>281000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>211100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>200900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>138800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>188300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>155600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>148600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>102400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>150900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>120600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>109400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>82000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>135300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>109000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>115400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>78700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>113400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>98600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>105700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>78100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>109000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>100800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>75400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>201700</v>
+      </c>
+      <c r="E10" s="3">
         <v>326400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>277700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>264300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>194800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>315200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>251300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>214800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>161900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>167000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>222500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>219100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>154800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>254800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>207000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>209200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>145200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>224900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>174000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>137500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>92400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>162300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>120100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>116300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>76700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>127800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>97500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>100600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>57200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>93100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>82200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>73000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1140,29 +1153,30 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>21100</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>15500</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1241,8 +1255,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,8 +1359,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1359,8 +1379,8 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>2000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1371,8 +1391,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1443,38 +1463,41 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E15" s="3">
         <v>29200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>12100</v>
       </c>
       <c r="F15" s="3">
         <v>12100</v>
       </c>
       <c r="G15" s="3">
-        <v>11500</v>
+        <v>12100</v>
       </c>
       <c r="H15" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I15" s="3">
         <v>29800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11400</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1544,8 +1567,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,210 +1604,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>329500</v>
+      </c>
+      <c r="E17" s="3">
         <v>464000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>408800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>396100</v>
       </c>
-      <c r="G17" s="3">
-        <v>315600</v>
-      </c>
       <c r="H17" s="3">
+        <v>313600</v>
+      </c>
+      <c r="I17" s="3">
         <v>421600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>371700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>352200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>287700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>491700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>365100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>351700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>260300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>349400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>293900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>285200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>207500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>294300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>224500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>200400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>158300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>285600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>195100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>196700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>146600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>203600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>168000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>173100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>132000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>178200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>158300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>130700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E18" s="3">
         <v>82500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>69600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>67400</v>
       </c>
-      <c r="G18" s="3">
-        <v>25800</v>
-      </c>
       <c r="H18" s="3">
+        <v>27800</v>
+      </c>
+      <c r="I18" s="3">
         <v>98200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>61900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>50300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>15100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-43700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>68500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>68300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>33300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>93700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>68700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>72500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>40100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>81500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>70100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>46500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>16200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>34000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>35000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>8800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>37600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>28100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>33200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>23900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>24700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>17700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,210 +1850,217 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>13500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>6500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-300</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-100</v>
       </c>
       <c r="AE20" s="3">
         <v>-100</v>
       </c>
       <c r="AF20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E21" s="3">
         <v>98100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>85800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>79900</v>
       </c>
-      <c r="G21" s="3">
-        <v>33200</v>
-      </c>
       <c r="H21" s="3">
+        <v>30800</v>
+      </c>
+      <c r="I21" s="3">
         <v>132200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>69000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>63400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-25900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>71200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>72400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>42800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>101700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>76000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>78900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>47300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>90300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>77500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>55100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>22000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>19200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>41100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>42300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>15400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>43200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>34200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>39300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>28900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>30600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>23500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2030,35 +2070,35 @@
       <c r="E22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>-700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>800</v>
       </c>
       <c r="P22" s="3">
         <v>800</v>
@@ -2070,260 +2110,269 @@
         <v>800</v>
       </c>
       <c r="S22" s="3">
+        <v>800</v>
+      </c>
+      <c r="T22" s="3">
         <v>900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>5300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>5700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>6100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>6800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>7800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E23" s="3">
         <v>69100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>74100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>67300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>103000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>57600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>50800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-38500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>59700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>61600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>33400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>92200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>66700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>70600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>38900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>81100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>68100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>44800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>11200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>28400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>29400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>29900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>20200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>24500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>14700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>16500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>10900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E24" s="3">
         <v>16000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>17800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>16900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>24400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-10800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>19300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>13700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>18800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>16600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>11300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>7100</v>
       </c>
       <c r="Z24" s="3">
         <v>7100</v>
       </c>
       <c r="AA24" s="3">
+        <v>7100</v>
+      </c>
+      <c r="AB24" s="3">
         <v>600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>5200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,210 +2472,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E26" s="3">
         <v>53200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>56300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>50400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>78600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>42700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>38100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-27700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>45500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>46300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>25700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>72900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>53000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>56200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>30500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>62400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>51400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>33500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>8500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>21300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>22200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>25200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>17000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>18800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>9700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>11300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>7100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E27" s="3">
         <v>53200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>56300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>50400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>78600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>42700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>38100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>45500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>46300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>25700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>72900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>53000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>56200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>30500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>62400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>51400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>33500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>8500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>21300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>22200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>25200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>17000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>18800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>9700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>11300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>7000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2784,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2797,17 +2858,17 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2815,20 +2876,23 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +2992,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,210 +3096,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-13500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-6500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>300</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>200</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>100</v>
       </c>
       <c r="AE32" s="3">
         <v>100</v>
       </c>
       <c r="AF32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG32" s="3">
         <v>600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E33" s="3">
         <v>53200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>56300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>50400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>78600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>42700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>38100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>45500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>46300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>25700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>72900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>53000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>56200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>30500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>62400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>51400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>33500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>21300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>22200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>25200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>17000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>18800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>11300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>7000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3408,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E35" s="3">
         <v>53200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>56300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>50400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>78600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>42700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>38100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>45500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>46300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>25700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>72900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>53000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>56200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>30500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>62400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>51400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>33500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>21300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>22200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>25200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>17000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>18800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>11300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>7000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45654</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44562</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44380</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44289</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44198</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44009</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43918</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43827</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43736</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43554</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43463</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43372</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43099</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42917</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3661,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,109 +3699,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E41" s="3">
         <v>358800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>280500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>212900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>173900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>439000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>281400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>223100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>167800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>234700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>77800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>92000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>100300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>312200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>259300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>233800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>190300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>253300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>234800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>127500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>118200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>72500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>34600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>38000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>19000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>80100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>52100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>71300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>60400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>53700</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3815,412 +3905,427 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>120500</v>
+      </c>
+      <c r="E43" s="3">
         <v>120200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>143700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>159100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>108400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>95800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>127900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>131600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>95600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>79400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>93900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>94300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>83000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>109500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>83300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>81900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>67100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>65400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>71200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>85900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>60200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>82700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>74800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>75900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>63000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>59300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>61900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>65400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>60400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>67200</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>330500</v>
+      </c>
+      <c r="E44" s="3">
         <v>310100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>370200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>378300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>363900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>337200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>341300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>322000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>347000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>371400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>439400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>490000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>413000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>318900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>266000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>221700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>183900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>140100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>134600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>138800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>202400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>185700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>209200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>181400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>164300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>145400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>157700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>149400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>158500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>175100</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E45" s="3">
         <v>5300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>40800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>29600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>24500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>14100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>19900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>19600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>13300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>17800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>20100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>12200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>13000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>11100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>10500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7100</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>767200</v>
+      </c>
+      <c r="E46" s="3">
         <v>826800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>846300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>807200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>703200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>914400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>791300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>721900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>654900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>718900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>644700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>717000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>635900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>770200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>632200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>561200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>465700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>476500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>454700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>367400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>400600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>360500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>331800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>313000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>266400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>297000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>284600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>297300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>289900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>303000</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4248,8 +4353,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4320,210 +4425,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>219600</v>
+      </c>
+      <c r="E48" s="3">
         <v>204500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>213000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>212300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>207100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>208300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>192600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>189500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>179300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>180000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>183700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>183800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>179700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>174000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>163000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>153700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>119100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>112200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>110000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>112300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>116300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>120400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>81200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>80000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>78200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>74100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>72400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>71100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>71500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>73800</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>246500</v>
+      </c>
+      <c r="E49" s="3">
         <v>244600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>210800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>209800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>206800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>171900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>168400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>165200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>155100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>153700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>152400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>152100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>151400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>149600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>148400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>147200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>146500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>146400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>145900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>145800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>145700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>145100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>145000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>144700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>144300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>134300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>135400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>133700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>130300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>128600</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4737,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,109 +4841,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E52" s="3">
         <v>10200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>3000</v>
       </c>
       <c r="F52" s="3">
         <v>3000</v>
       </c>
       <c r="G52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H52" s="3">
         <v>2700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>900</v>
       </c>
       <c r="J52" s="3">
         <v>900</v>
       </c>
       <c r="K52" s="3">
+        <v>900</v>
+      </c>
+      <c r="L52" s="3">
         <v>17300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>24100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2400</v>
-      </c>
-      <c r="N52" s="3">
-        <v>2500</v>
       </c>
       <c r="O52" s="3">
         <v>2500</v>
       </c>
       <c r="P52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Q52" s="3">
         <v>2600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1900</v>
-      </c>
-      <c r="T52" s="3">
-        <v>2000</v>
       </c>
       <c r="U52" s="3">
         <v>2000</v>
       </c>
       <c r="V52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W52" s="3">
         <v>1900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11000</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,109 +5049,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1237900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1286100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1273200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1232300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1119800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1297200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1155900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1085400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1006500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1076800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>983200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1055400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>969500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1096400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>945500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>864000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>733300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>737100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>712600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>627500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>666800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>629500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>559700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>540400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>495800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>514200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>502600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>510400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>502200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>516400</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5193,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,144 +5231,148 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>137600</v>
+      </c>
+      <c r="E57" s="3">
         <v>158500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>148200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>175200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>139100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>190400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>179100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>143400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>101700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>140800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>122800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>204100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>167400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>191300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>166100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>145700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>120000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>123600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>101900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>41400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>74400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>83800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>105500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>101500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>78200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>68700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>76900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>73500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>51600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>40300</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E58" s="3">
         <v>26100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>23700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>22800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>22100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>17900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>35700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24400</v>
-      </c>
-      <c r="N58" s="3">
-        <v>24600</v>
       </c>
       <c r="O58" s="3">
         <v>24600</v>
@@ -5247,43 +5381,43 @@
         <v>24600</v>
       </c>
       <c r="Q58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="R58" s="3">
         <v>24500</v>
       </c>
       <c r="S58" s="3">
-        <v>22700</v>
+        <v>24500</v>
       </c>
       <c r="T58" s="3">
         <v>22700</v>
       </c>
       <c r="U58" s="3">
+        <v>22700</v>
+      </c>
+      <c r="V58" s="3">
         <v>20800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>18900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>17100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>15200</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>42100</v>
       </c>
       <c r="Z58" s="3">
         <v>42100</v>
       </c>
       <c r="AA58" s="3">
-        <v>43600</v>
+        <v>42100</v>
       </c>
       <c r="AB58" s="3">
         <v>43600</v>
       </c>
       <c r="AC58" s="3">
-        <v>47100</v>
+        <v>43600</v>
       </c>
       <c r="AD58" s="3">
         <v>47100</v>
@@ -5294,8 +5428,8 @@
       <c r="AF58" s="3">
         <v>47100</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>8</v>
+      <c r="AG58" s="3">
+        <v>47100</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>8</v>
@@ -5303,412 +5437,427 @@
       <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E59" s="3">
         <v>100000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>73700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>73500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>79800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>96700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>83100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>118200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>92900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>243600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>128400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>162700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>158100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>187800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>139200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>133800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>110300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>141400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>96900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>70800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>59100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>71300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>53400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>54500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>50600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>75000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>62100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>52100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>51900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>64500</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>297200</v>
+      </c>
+      <c r="E60" s="3">
         <v>379500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>328100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>351900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>298800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>398400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>360800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>344900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>329800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>409000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>275600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>391400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>350100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>403700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>329900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>304000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>253000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>287800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>219600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>131200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>150600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>170300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>201100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>198200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>172500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>187300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>186000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>172600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>150600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>151900</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E61" s="3">
         <v>146400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>154300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>154000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>152800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>154800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>139700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>138400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>119900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>71700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>77800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>83600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>89600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>95700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>101700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>107800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>105500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>111000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>215800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>270800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>326300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>281700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>252700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>263300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>273800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>284400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>340700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>380800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>418000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>428600</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E62" s="3">
         <v>20100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>19500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>20400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>69500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>79200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>80500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>83500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>79100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>74300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>68100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>53400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>49900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>54600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>56400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>58300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>55500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>18000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>15100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>14000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>13500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>13000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>13800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>12600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>12100</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +5957,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6061,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,109 +6165,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>473600</v>
+      </c>
+      <c r="E66" s="3">
         <v>546000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>503200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>526400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>472900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>573600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>517100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>498200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>464000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>550300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>432600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>555500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>523200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>578500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>505900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>479900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>412000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>448600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>489900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>458400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>535100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>507500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>471800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>476500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>460300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>485200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>539800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>567200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>581200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>592700</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6309,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6411,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6515,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6451,8 +6619,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,109 +6723,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>630700</v>
+      </c>
+      <c r="E72" s="3">
         <v>614100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>561000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>504700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>454300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>438400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>359800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>317200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>279100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>268600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>296300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>250800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>204500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>178900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>106000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>53000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-33700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-96100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-147600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-181100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-189500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-194300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-215500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-237600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-240100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-265100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-281800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-300000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-296200</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +6931,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7035,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,109 +7139,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>764300</v>
+      </c>
+      <c r="E76" s="3">
         <v>740100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>770000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>705900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>646900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>723600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>638800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>587200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>542600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>526500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>550700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>499900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>446400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>517800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>439600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>384100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>321300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>288400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>222600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>169000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>131600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>122000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>87900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>64000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>35500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>29000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-37200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-56800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-79000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-76200</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7347,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45654</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44562</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44380</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44289</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44198</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44009</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43918</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43827</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43736</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43554</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43463</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43372</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43099</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42917</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E81" s="3">
         <v>53200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>56300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>50400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>78600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>42700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>38100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>45500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>46300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>25700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>72900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>53000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>56200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>30500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>62400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>51400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>33500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>21300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>22200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>25200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>17000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>18800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>11300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>7000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,67 +7600,68 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E83" s="3">
         <v>6700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>9800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7500</v>
-      </c>
-      <c r="V83" s="3">
-        <v>7700</v>
       </c>
       <c r="W83" s="3">
         <v>7700</v>
@@ -7471,40 +7670,43 @@
         <v>7700</v>
       </c>
       <c r="Y83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="Z83" s="3">
         <v>7400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>7300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>6500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>6600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>6300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>6200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>4600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +7806,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7910,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8014,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8118,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,109 +8222,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-80300</v>
+      </c>
+      <c r="E89" s="3">
         <v>225600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>83500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>56000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-103700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>171200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>86000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>75500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-46700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>173100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>14000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-88600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>73300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>51000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>62500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-40300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>127300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>166700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>68500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>60300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>16800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>39800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-30000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>57200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>35200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>58300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>25300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>72200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>65600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>21600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-16100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,109 +8366,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7500</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-8400</v>
       </c>
       <c r="AA91" s="3">
         <v>-8400</v>
       </c>
       <c r="AB91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8572,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,109 +8676,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-44400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-58000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-17800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-6200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,8 +8820,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8616,8 +8850,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8656,11 +8890,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-600</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -8688,8 +8922,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9026,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9130,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,187 +9234,193 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-101700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-102800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-107600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-7100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-102800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-53500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-52600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>45700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-12900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-21500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-45100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-37900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>18300</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>2700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
@@ -9182,116 +9431,122 @@
         <v>0</v>
       </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>100</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-99800</v>
+      </c>
+      <c r="E102" s="3">
         <v>78300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>67500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>39000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-265000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>157600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>58200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>55300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-66900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>157000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-211900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>52900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>25500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>43500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-63000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>107300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>45700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>38000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>19000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-61000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>28000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>10900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>18900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>19400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-9700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>YETI</t>
   </si>
@@ -656,468 +656,481 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45654</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44562</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44380</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44289</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44198</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44009</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43827</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43736</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43645</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43554</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43463</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43372</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43099</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>445900</v>
+      </c>
+      <c r="E8" s="3">
         <v>351100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>546500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>478400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>463500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>341400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>519800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>433600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>402600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>302800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>448000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>433600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>420000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>293600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>443100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>362600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>357700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>247600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>375800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>294600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>246900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>174400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>297600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>229100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>231700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>155400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>241200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>196100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>206300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>135300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>202100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>183000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>148400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>188300</v>
+      </c>
+      <c r="E9" s="3">
         <v>149400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>220100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>200700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>199200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>146600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>204600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>182300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>187700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>140900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>281000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>211100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>200900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>138800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>188300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>155600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>148600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>102400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>150900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>120600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>109400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>82000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>135300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>109000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>115400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>78700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>113400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>98600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>105700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>78100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>109000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>100800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>75400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>257600</v>
+      </c>
+      <c r="E10" s="3">
         <v>201700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>326400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>277700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>264300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>194800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>315200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>251300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>214800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>161900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>167000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>222500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>219100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>154800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>254800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>207000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>209200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>145200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>224900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>174000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>137500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>92400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>162300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>120100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>116300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>76700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>127800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>97500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>100600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>57200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>93100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>82200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1154,32 +1167,33 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>21100</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>15500</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1258,8 +1272,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1362,8 +1379,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1379,12 +1399,12 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1394,8 +1414,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1466,41 +1486,44 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E15" s="3">
         <v>8100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>29200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>12100</v>
       </c>
       <c r="G15" s="3">
         <v>12100</v>
       </c>
       <c r="H15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I15" s="3">
         <v>7100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>29800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11400</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1570,8 +1593,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1605,216 +1631,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>383900</v>
+      </c>
+      <c r="E17" s="3">
         <v>329500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>464000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>408800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>396100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>313600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>421600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>371700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>352200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>287700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>491700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>365100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>351700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>260300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>349400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>293900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>285200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>207500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>294300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>224500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>200400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>158300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>285600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>195100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>196700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>146600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>203600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>168000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>173100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>132000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>178200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>158300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>130700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E18" s="3">
         <v>21700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>82500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>69600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>67400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>27800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>98200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>61900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>50300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-43700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>68500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>68300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>33300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>93700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>68700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>72500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>40100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>81500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>70100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>46500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>16200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>34000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>35000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>37600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>28100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>33200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>23900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>24700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>17700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1851,216 +1884,223 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>13500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>6500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-300</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-200</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-100</v>
       </c>
       <c r="AF20" s="3">
         <v>-100</v>
       </c>
       <c r="AG20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E21" s="3">
         <v>31100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>98100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>85800</v>
       </c>
-      <c r="G21" s="3">
-        <v>79900</v>
-      </c>
       <c r="H21" s="3">
+        <v>75300</v>
+      </c>
+      <c r="I21" s="3">
         <v>30800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>132200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>69000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>63400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-25900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>71200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>72400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>42800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>101700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>76000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>78900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>47300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>90300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>77500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>55100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>22000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>19200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>41100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>42300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>15400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>43200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>34200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>39300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>28900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>30600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>23500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2073,35 +2113,35 @@
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3">
         <v>-700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>800</v>
       </c>
       <c r="Q22" s="3">
         <v>800</v>
@@ -2113,266 +2153,275 @@
         <v>800</v>
       </c>
       <c r="T22" s="3">
+        <v>800</v>
+      </c>
+      <c r="U22" s="3">
         <v>900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>5300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>6100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>6800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E23" s="3">
         <v>23400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>69100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>74100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>67300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>22400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>103000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>57600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>50800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-38500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>59700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>61600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>33400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>92200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>66700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>70600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>38900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>81100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>68100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>44800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>11200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>28400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>29400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>29900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>20200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>24500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>14700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>16500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E24" s="3">
         <v>6700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>17800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>24400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-10800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>15300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>19300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>14400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>18800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>16600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>11300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>7100</v>
       </c>
       <c r="AA24" s="3">
         <v>7100</v>
       </c>
       <c r="AB24" s="3">
+        <v>7100</v>
+      </c>
+      <c r="AC24" s="3">
         <v>600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>5000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2475,216 +2524,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E26" s="3">
         <v>16600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>53200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>56300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>50400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>78600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>42700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>38100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-27700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>45500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>46300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>25700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>72900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>53000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>56200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>30500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>62400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>51400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>33500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>8500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>21300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>22200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>25200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>17000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>18800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>9700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>11300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E27" s="3">
         <v>16600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>53200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>56300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>50400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>78600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>42700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>38100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>45500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>46300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>25700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>72900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>53000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>56200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>30500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>62400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>51400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>33500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>8500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>21300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>22200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>25200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>17000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>18800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>9700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>11300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2787,8 +2845,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2861,17 +2922,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2879,20 +2940,23 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2995,8 +3059,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3099,216 +3166,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E32" s="3">
         <v>1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-13500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-6500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>300</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>200</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>100</v>
       </c>
       <c r="AF32" s="3">
         <v>100</v>
       </c>
       <c r="AG32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH32" s="3">
         <v>600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E33" s="3">
         <v>16600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>53200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>56300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>50400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>78600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>42700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>38100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>45500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>46300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>25700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>72900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>53000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>56200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>30500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>62400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>51400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>33500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>8500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>21300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>22200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>25200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>17000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>18800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>11300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3411,221 +3487,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E35" s="3">
         <v>16600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>53200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>56300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>50400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>78600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>42700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>38100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>45500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>46300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>25700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>72900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>53000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>56200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>30500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>62400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>51400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>33500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>8500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>21300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>22200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>25200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>17000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>18800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>11300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45654</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44562</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44380</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44289</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44198</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44009</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43827</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43736</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43645</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43554</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43463</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43372</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43099</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3662,8 +3747,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3700,112 +3786,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>269700</v>
+      </c>
+      <c r="E41" s="3">
         <v>259000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>358800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>280500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>212900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>173900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>439000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>281400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>223100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>167800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>234700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>77800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>92000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>100300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>312200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>259300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>233800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>190300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>253300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>234800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>127500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>118200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>72500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>34600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>38000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>19000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>80100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>52100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>71300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>60400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>53700</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3908,424 +3998,439 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>163600</v>
+      </c>
+      <c r="E43" s="3">
         <v>120500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>120200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>143700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>159100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>108400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>95800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>127900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>131600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>95600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>79400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>93900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>94300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>83000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>109500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>83300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>81900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>67100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>65400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>71200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>85900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>60200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>82700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>74800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>75900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>63000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>59300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>61900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>65400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>60400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>67200</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>342100</v>
+      </c>
+      <c r="E44" s="3">
         <v>330500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>310100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>370200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>378300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>363900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>337200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>341300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>322000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>347000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>371400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>439400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>490000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>413000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>318900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>266000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>221700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>183900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>140100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>134600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>138800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>202400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>185700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>209200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>181400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>164300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>145400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>157700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>149400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>158500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>175100</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E45" s="3">
         <v>6200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>40800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>39600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>29600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>23800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>24500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>19900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>19600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>13300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>17800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>20100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>12200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>13000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>11100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>10500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>7100</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>828200</v>
+      </c>
+      <c r="E46" s="3">
         <v>767200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>826800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>846300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>807200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>703200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>914400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>791300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>721900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>654900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>718900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>644700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>717000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>635900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>770200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>632200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>561200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>465700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>476500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>454700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>367400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>400600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>360500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>331800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>313000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>266400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>297000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>284600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>297300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>289900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>303000</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4356,8 +4461,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4428,216 +4533,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>223000</v>
+      </c>
+      <c r="E48" s="3">
         <v>219600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>204500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>213000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>212300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>207100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>208300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>192600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>189500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>179300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>180000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>183700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>183800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>179700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>174000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>163000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>153700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>119100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>112200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>110000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>112300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>116300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>120400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>81200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>80000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>78200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>74100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>72400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>71100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>71500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>73800</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>248500</v>
+      </c>
+      <c r="E49" s="3">
         <v>246500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>244600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>210800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>209800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>206800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>171900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>168400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>165200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>155100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>153700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>152400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>152100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>151400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>149600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>148400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>147200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>146500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>146400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>145900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>145800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>145700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>145100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>145000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>144700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>144300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>134300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>135400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>133700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>130300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>128600</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4740,8 +4854,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4844,8 +4961,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4853,103 +4973,106 @@
         <v>1200</v>
       </c>
       <c r="E52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F52" s="3">
         <v>10200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>3000</v>
       </c>
       <c r="G52" s="3">
         <v>3000</v>
       </c>
       <c r="H52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I52" s="3">
         <v>2700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>900</v>
       </c>
       <c r="K52" s="3">
         <v>900</v>
       </c>
       <c r="L52" s="3">
+        <v>900</v>
+      </c>
+      <c r="M52" s="3">
         <v>17300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>24100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2400</v>
-      </c>
-      <c r="O52" s="3">
-        <v>2500</v>
       </c>
       <c r="P52" s="3">
         <v>2500</v>
       </c>
       <c r="Q52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R52" s="3">
         <v>2600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1900</v>
-      </c>
-      <c r="U52" s="3">
-        <v>2000</v>
       </c>
       <c r="V52" s="3">
         <v>2000</v>
       </c>
       <c r="W52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X52" s="3">
         <v>1900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>8800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11000</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5052,112 +5175,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1303000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1237900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1286100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1273200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1232300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1119800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1297200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1155900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1085400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1006500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1076800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>983200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1055400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>969500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1096400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>945500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>864000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>733300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>737100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>712600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>627500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>666800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>629500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>559700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>540400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>495800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>514200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>502600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>510400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>502200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>516400</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5194,8 +5323,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5232,112 +5362,116 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>152300</v>
+      </c>
+      <c r="E57" s="3">
         <v>137600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>158500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>148200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>175200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>139100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>190400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>179100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>143400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>101700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>140800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>122800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>204100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>167400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>191300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>166100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>145700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>120000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>123600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>101900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>41400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>74400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>83800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>105500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>101500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>78200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>68700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>76900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>73500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>51600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>40300</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5345,37 +5479,37 @@
         <v>27400</v>
       </c>
       <c r="E58" s="3">
+        <v>27400</v>
+      </c>
+      <c r="F58" s="3">
         <v>26100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>23700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>22800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>22100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>21300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>19900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>35700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>24400</v>
-      </c>
-      <c r="O58" s="3">
-        <v>24600</v>
       </c>
       <c r="P58" s="3">
         <v>24600</v>
@@ -5384,43 +5518,43 @@
         <v>24600</v>
       </c>
       <c r="R58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="S58" s="3">
         <v>24500</v>
       </c>
       <c r="T58" s="3">
-        <v>22700</v>
+        <v>24500</v>
       </c>
       <c r="U58" s="3">
         <v>22700</v>
       </c>
       <c r="V58" s="3">
+        <v>22700</v>
+      </c>
+      <c r="W58" s="3">
         <v>20800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>18900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>17100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>15200</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>42100</v>
       </c>
       <c r="AA58" s="3">
         <v>42100</v>
       </c>
       <c r="AB58" s="3">
-        <v>43600</v>
+        <v>42100</v>
       </c>
       <c r="AC58" s="3">
         <v>43600</v>
       </c>
       <c r="AD58" s="3">
-        <v>47100</v>
+        <v>43600</v>
       </c>
       <c r="AE58" s="3">
         <v>47100</v>
@@ -5431,8 +5565,8 @@
       <c r="AG58" s="3">
         <v>47100</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>8</v>
+      <c r="AH58" s="3">
+        <v>47100</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>8</v>
@@ -5440,424 +5574,439 @@
       <c r="AJ58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E59" s="3">
         <v>70500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>100000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>73700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>73500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>79800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>96700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>83100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>118200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>92900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>243600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>128400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>162700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>158100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>187800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>139200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>133800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>110300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>141400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>96900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>70800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>59100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>71300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>53400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>54500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>50600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>75000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>62100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>52100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>51900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>64500</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>329000</v>
+      </c>
+      <c r="E60" s="3">
         <v>297200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>379500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>328100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>351900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>298800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>398400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>360800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>344900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>329800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>409000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>275600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>391400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>350100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>403700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>329900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>304000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>253000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>287800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>219600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>131200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>150600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>170300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>201100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>198200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>172500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>187300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>186000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>172600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>150600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>151900</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>149600</v>
+      </c>
+      <c r="E61" s="3">
         <v>155700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>146400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>154300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>154000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>152800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>154800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>139700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>138400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>119900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>71700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>77800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>83600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>89600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>95700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>101700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>107800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>105500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>111000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>215800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>270800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>326300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>281700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>252700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>263300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>273800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>284400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>340700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>380800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>418000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>428600</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E62" s="3">
         <v>20700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>19500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>20400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>69500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>79200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>80500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>83500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>79100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>74300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>68100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>53400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>49900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>54600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>56400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>58300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>55500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>18000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>15100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>14000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>13500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>13000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>13800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>12600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>12100</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5960,8 +6109,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6064,8 +6216,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6168,112 +6323,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>500300</v>
+      </c>
+      <c r="E66" s="3">
         <v>473600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>546000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>503200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>526400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>472900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>573600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>517100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>498200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>464000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>550300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>432600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>555500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>523200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>578500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>505900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>479900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>412000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>448600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>489900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>458400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>535100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>507500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>471800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>476500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>460300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>485200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>539800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>567200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>581200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>592700</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6310,8 +6471,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6414,8 +6576,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6518,8 +6683,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6622,8 +6790,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6726,112 +6897,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>681900</v>
+      </c>
+      <c r="E72" s="3">
         <v>630700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>614100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>561000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>504700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>454300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>438400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>359800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>317200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>279100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>268600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>296300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>250800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>204500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>178900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>106000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>53000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-33700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-96100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-147600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-181100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-189500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-194300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-215500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-237600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-240100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-265100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-281800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-300000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-296200</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6934,8 +7111,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7038,8 +7218,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7142,112 +7325,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>802700</v>
+      </c>
+      <c r="E76" s="3">
         <v>764300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>740100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>770000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>705900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>646900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>723600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>638800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>587200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>542600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>526500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>550700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>499900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>446400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>517800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>439600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>384100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>321300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>288400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>222600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>169000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>131600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>122000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>87900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>64000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>35500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>29000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-37200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-56800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-79000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-76200</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7350,221 +7539,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45654</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44562</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44380</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44289</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44198</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44009</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43827</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43736</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43645</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43554</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43463</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43372</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43099</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E81" s="3">
         <v>16600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>53200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>56300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>50400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>78600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>42700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>38100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>45500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>46300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>25700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>72900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>53000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>56200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>30500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>62400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>51400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>33500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>8500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>21300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>22200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>25200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>17000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>18800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>11300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7601,70 +7799,71 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E83" s="3">
         <v>11500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7500</v>
-      </c>
-      <c r="W83" s="3">
-        <v>7700</v>
       </c>
       <c r="X83" s="3">
         <v>7700</v>
@@ -7673,40 +7872,43 @@
         <v>7700</v>
       </c>
       <c r="Z83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AA83" s="3">
         <v>7400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>7300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>6500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>6600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>6300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>6200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>4600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7809,8 +8011,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7913,8 +8118,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8017,8 +8225,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8121,8 +8332,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8225,112 +8439,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-80300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>225600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>83500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>56000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-103700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>171200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>86000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>75500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-46700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>173100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-88600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>73300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>51000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>62500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-40300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>127300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>166700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>68500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>60300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>16800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>39800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-30000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>57200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>35200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>58300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>25300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>72200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>65600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>21600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-16100</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8367,112 +8587,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-7500</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-8400</v>
       </c>
       <c r="AB91" s="3">
         <v>-8400</v>
       </c>
       <c r="AC91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8575,8 +8799,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8679,112 +8906,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-44400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-58000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-18700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-18100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-14800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-9500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-6200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8821,8 +9054,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8853,8 +9087,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8893,11 +9127,11 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-600</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -8925,8 +9159,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9029,8 +9266,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9133,8 +9373,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9237,193 +9480,199 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-33900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-101700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-102800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-107600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-7100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-102800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-53500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-52600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>45700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-12900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-21500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-45100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-37900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>18300</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
@@ -9434,119 +9683,125 @@
         <v>0</v>
       </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>100</v>
       </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-99800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>78300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>67500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>39000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-265000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>157600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>58200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>55300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-66900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>157000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-211900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>52900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>25500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>43500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-63000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>18500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>107300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>9200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>45700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>38000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>19000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-61000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>28000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>10900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>18900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>19400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-9700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>YETI</t>
   </si>
@@ -656,494 +656,507 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45654</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45290</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44562</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44380</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44289</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44198</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44009</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43918</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43827</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43736</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43645</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43554</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43463</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43372</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42917</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>583700</v>
+      </c>
+      <c r="E8" s="3">
         <v>487800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>445900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>351100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>546500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>478400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>463500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>341400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>519800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>433600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>402600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>302800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>448000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>433600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>420000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>293600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>443100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>362600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>357700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>247600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>375800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>294600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>246900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>174400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>297600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>229100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>231700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>155400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>241200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>196100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>206300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>135300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>202100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>183000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>148400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>242800</v>
+      </c>
+      <c r="E9" s="3">
         <v>215200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>188300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>149400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>220100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>200700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>199200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>146600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>204600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>182300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>187700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>140900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>281000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>211100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>200900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>138800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>188300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>155600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>148600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>102400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>150900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>120600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>109400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>82000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>135300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>109000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>115400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>78700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>113400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>98600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>105700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>78100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>109000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>100800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>75400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>340900</v>
+      </c>
+      <c r="E10" s="3">
         <v>272500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>257600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>201700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>326400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>277700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>264300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>194800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>315200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>251300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>214800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>161900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>167000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>222500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>219100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>154800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>254800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>207000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>209200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>145200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>224900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>174000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>137500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>92400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>162300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>120100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>116300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>76700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>127800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>97500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>100600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>57200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>93100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>82200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>73000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1182,13 +1195,14 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>25200</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1196,24 +1210,24 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>21100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>15500</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1292,8 +1306,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1402,13 +1419,16 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-1200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1416,21 +1436,21 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>-2000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1440,8 +1460,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1512,47 +1532,50 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E15" s="3">
         <v>13800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>29200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>29800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11400</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1622,8 +1645,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1659,228 +1685,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>509400</v>
+      </c>
+      <c r="E17" s="3">
         <v>433400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>383900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>329500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>466100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>408800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>396100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>313600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>421600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>371700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>352200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>287700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>491700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>365100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>351700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>260300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>349400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>293900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>285200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>207500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>294300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>224500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>200400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>158300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>285600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>195100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>196700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>146600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>203600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>168000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>173100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>132000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>178200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>158300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>130700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E18" s="3">
         <v>54400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>62000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>21700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>80500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>69600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>67400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>27800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>98200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>61900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>50300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-43700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>68500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>68300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>33300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>93700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>68700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>72500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>40100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>81500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>70100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>46500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>16200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>12000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>34000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>35000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>8800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>37600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>28100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>33200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>23900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>24700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>17700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1919,237 +1952,244 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>13500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>4100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>6500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-300</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-200</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-100</v>
       </c>
       <c r="AH20" s="3">
         <v>-100</v>
       </c>
       <c r="AI20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>109400</v>
+      </c>
+      <c r="E21" s="3">
         <v>66900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>76000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>31100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>96100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>85800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>75300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>30800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>132200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>69000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>63400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-25900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>71200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>72400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>42800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>101700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>76000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>78900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>47300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>90300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>77500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>55100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>22000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>19200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>41100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>42300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>15400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>43200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>34200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>39300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>8900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>28900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>30600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>23500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>400</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2159,35 +2199,35 @@
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>-700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>800</v>
       </c>
       <c r="S22" s="3">
         <v>800</v>
@@ -2199,278 +2239,287 @@
         <v>800</v>
       </c>
       <c r="V22" s="3">
+        <v>800</v>
+      </c>
+      <c r="W22" s="3">
         <v>900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>4700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>5300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>5700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>6100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>8100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>75700</v>
+      </c>
+      <c r="E23" s="3">
         <v>53100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>68100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>69100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>74100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>67300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>103000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>57600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>50800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-38500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>59700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>61600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>33400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>92200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>66700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>70600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>38900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>81100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>68100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>44800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>11200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>28400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>29400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>29900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>20200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>24500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>14700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>16500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>10900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E24" s="3">
         <v>13700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>17800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>16900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>24400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-10800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>19300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>13700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>14400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>18800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>16600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>11300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2000</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>7100</v>
       </c>
       <c r="AC24" s="3">
         <v>7100</v>
       </c>
       <c r="AD24" s="3">
+        <v>7100</v>
+      </c>
+      <c r="AE24" s="3">
         <v>600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>5700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>5200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>3800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2579,228 +2628,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E26" s="3">
         <v>39400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>51200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>53200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>56300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>50400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>78600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>42700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>38100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-27700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>45500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>46300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>25700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>72900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>53000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>56200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>30500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>62400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>51400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>33500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>8500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>21300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>22200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>25200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>17000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>18800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>9700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>11300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>7100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E27" s="3">
         <v>39400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>51200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>53200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>56300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>50400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>78600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>42700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>38100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-27700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>45500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>46300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>25700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>72900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>53000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>56200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>30500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>62400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>51400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>33500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>8500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>21300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>22200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>25200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>17000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>18800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>9700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>11300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>7000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2909,8 +2967,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2989,17 +3050,17 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3007,20 +3068,23 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-5700</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3129,8 +3193,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3239,228 +3306,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-13500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-4100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-6500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>300</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>1000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>200</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>100</v>
       </c>
       <c r="AH32" s="3">
         <v>100</v>
       </c>
       <c r="AI32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E33" s="3">
         <v>39400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>51200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>53200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>56300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>50400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>78600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>42700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>38100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-27700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>45500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>46300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>25700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>72900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>53000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>56200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>30500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>62400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>51400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>33500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>8500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>21300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>22200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>25200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>17000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>18800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>11300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>7000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3569,233 +3645,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E35" s="3">
         <v>39400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>51200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>53200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>56300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>50400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>78600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>42700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>38100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-27700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>45500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>46300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>25700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>72900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>53000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>56200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>30500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>62400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>51400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>33500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>8500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>21300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>22200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>25200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>17000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>18800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>11300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>7000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45654</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45290</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44562</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44380</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44289</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44198</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44009</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43918</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43827</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43736</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43645</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43554</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43463</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43372</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42917</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3834,8 +3919,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3874,118 +3960,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>188300</v>
+      </c>
+      <c r="E41" s="3">
         <v>164500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>269700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>259000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>358800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>280500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>212900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>173900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>439000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>281400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>223100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>167800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>234700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>77800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>92000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>100300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>312200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>259300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>233800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>190300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>253300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>234800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>127500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>118200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>72500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>34600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>38000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>19000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>80100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>52100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>71300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>60400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>53700</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4094,448 +4184,463 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>141400</v>
+      </c>
+      <c r="E43" s="3">
         <v>157400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>163600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>120500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>120200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>143700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>159100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>108400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>95800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>127900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>131600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>95600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>79400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>93900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>94300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>83000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>109500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>83300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>81900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>67100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>65400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>71200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>85900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>60200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>82700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>74800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>75900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>63000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>59300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>61900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>65400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>60400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>67200</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>290600</v>
+      </c>
+      <c r="E44" s="3">
         <v>324000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>342100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>330500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>310100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>370200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>378300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>363900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>337200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>341300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>322000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>347000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>371400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>439400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>490000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>413000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>318900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>266000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>221700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>183900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>140100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>134600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>138800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>202400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>185700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>209200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>181400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>164300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>145400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>157700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>149400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>158500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>175100</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E45" s="3">
         <v>8900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>33300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>33600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>40800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>39600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>24500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>17700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>14100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>15300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>19900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>19600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>13300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>17800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>20100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>12200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>13000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>11100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>10500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>660300</v>
+      </c>
+      <c r="E46" s="3">
         <v>696700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>828200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>767200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>826800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>846300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>807200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>703200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>914400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>791300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>721900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>654900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>718900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>644700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>717000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>635900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>770200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>632200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>561200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>465700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>476500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>454700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>367400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>400600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>360500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>331800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>313000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>266400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>297000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>284600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>297300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>289900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>303000</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4572,8 +4677,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4644,228 +4749,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>273600</v>
+      </c>
+      <c r="E48" s="3">
         <v>268700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>223000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>219600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>204500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>213000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>212300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>207100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>208300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>192600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>189500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>179300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>180000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>183700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>183800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>179700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>174000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>163000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>153700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>119100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>112200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>110000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>112300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>116300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>120400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>81200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>80000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>78200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>74100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>72400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>71100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>71500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>73800</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>292100</v>
+      </c>
+      <c r="E49" s="3">
         <v>286100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>248500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>246500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>244600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>210800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>209800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>206800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>171900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>168400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>165200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>155100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>153700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>152400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>152100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>151400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>149600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>148400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>147200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>146500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>146400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>145900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>145800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>145700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>145100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>145000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>144700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>144300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>134300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>135400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>133700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>130300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>128600</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4974,8 +5088,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5084,118 +5201,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E52" s="3">
         <v>8700</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1200</v>
       </c>
       <c r="F52" s="3">
         <v>1200</v>
       </c>
       <c r="G52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H52" s="3">
         <v>10200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>3000</v>
       </c>
       <c r="I52" s="3">
         <v>3000</v>
       </c>
       <c r="J52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K52" s="3">
         <v>2700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2600</v>
-      </c>
-      <c r="L52" s="3">
-        <v>900</v>
       </c>
       <c r="M52" s="3">
         <v>900</v>
       </c>
       <c r="N52" s="3">
+        <v>900</v>
+      </c>
+      <c r="O52" s="3">
         <v>17300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>24100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2400</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>2500</v>
       </c>
       <c r="R52" s="3">
         <v>2500</v>
       </c>
       <c r="S52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="T52" s="3">
         <v>2600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1900</v>
-      </c>
-      <c r="W52" s="3">
-        <v>2000</v>
       </c>
       <c r="X52" s="3">
         <v>2000</v>
       </c>
       <c r="Y52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z52" s="3">
         <v>1900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>8800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>10100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>10600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5304,118 +5427,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1235400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1260100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1303000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1237900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1286100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1273200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1232300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1119800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1297200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1155900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1085400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1006500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1076800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>983200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1055400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>969500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1096400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>945500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>864000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>733300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>737100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>712600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>627500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>666800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>629500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>559700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>540400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>495800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>514200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>502600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>510400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>502200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>516400</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5454,8 +5583,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5494,162 +5624,166 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>140200</v>
+      </c>
+      <c r="E57" s="3">
         <v>146700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>152300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>137600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>158500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>148200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>175200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>139100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>190400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>179100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>143400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>101700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>140800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>122800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>204100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>167400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>191300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>166100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>145700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>120000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>123600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>101900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>41400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>74400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>83800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>105500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>101500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>78200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>68700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>76900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>73500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>51600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>40300</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E58" s="3">
         <v>21900</v>
-      </c>
-      <c r="E58" s="3">
-        <v>27400</v>
       </c>
       <c r="F58" s="3">
         <v>27400</v>
       </c>
       <c r="G58" s="3">
+        <v>27400</v>
+      </c>
+      <c r="H58" s="3">
         <v>26100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>23700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>22800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>22100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>19900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>17900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>35700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>24600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>24400</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>24600</v>
       </c>
       <c r="R58" s="3">
         <v>24600</v>
@@ -5658,43 +5792,43 @@
         <v>24600</v>
       </c>
       <c r="T58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="U58" s="3">
         <v>24500</v>
       </c>
       <c r="V58" s="3">
-        <v>22700</v>
+        <v>24500</v>
       </c>
       <c r="W58" s="3">
         <v>22700</v>
       </c>
       <c r="X58" s="3">
+        <v>22700</v>
+      </c>
+      <c r="Y58" s="3">
         <v>20800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>18900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>17100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>15200</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>42100</v>
       </c>
       <c r="AC58" s="3">
         <v>42100</v>
       </c>
       <c r="AD58" s="3">
-        <v>43600</v>
+        <v>42100</v>
       </c>
       <c r="AE58" s="3">
         <v>43600</v>
       </c>
       <c r="AF58" s="3">
-        <v>47100</v>
+        <v>43600</v>
       </c>
       <c r="AG58" s="3">
         <v>47100</v>
@@ -5705,8 +5839,8 @@
       <c r="AI58" s="3">
         <v>47100</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>8</v>
+      <c r="AJ58" s="3">
+        <v>47100</v>
       </c>
       <c r="AK58" s="3" t="s">
         <v>8</v>
@@ -5714,448 +5848,463 @@
       <c r="AL58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>61700</v>
+      </c>
+      <c r="E59" s="3">
         <v>74800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>74200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>70500</v>
       </c>
-      <c r="G59" s="3">
-        <v>100000</v>
-      </c>
       <c r="H59" s="3">
+        <v>61900</v>
+      </c>
+      <c r="I59" s="3">
         <v>73700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>73500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>79800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>96700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>83100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>118200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>92900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>243600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>128400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>162700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>158100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>187800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>139200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>133800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>110300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>141400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>96900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>70800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>59100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>71300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>53400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>54500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>50600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>75000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>62100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>52100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>51900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>64500</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>334300</v>
+      </c>
+      <c r="E60" s="3">
         <v>322000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>329000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>297200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>379500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>328100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>351900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>298800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>398400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>360800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>344900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>329800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>409000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>275600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>391400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>350100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>403700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>329900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>304000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>253000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>287800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>219600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>131200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>150600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>170300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>201100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>198200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>172500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>187300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>186000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>172600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>150600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>151900</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>208200</v>
+      </c>
+      <c r="E61" s="3">
         <v>200700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>149600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>155700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>146400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>154300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>154000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>152800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>154800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>139700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>138400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>119900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>71700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>77800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>83600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>89600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>95700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>101700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>107800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>105500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>111000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>215800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>270800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>326300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>281700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>252700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>263300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>273800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>284400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>340700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>380800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>418000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>428600</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E62" s="3">
         <v>22000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20700</v>
       </c>
-      <c r="G62" s="3">
-        <v>20100</v>
-      </c>
       <c r="H62" s="3">
+        <v>19800</v>
+      </c>
+      <c r="I62" s="3">
         <v>19500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>69500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>79200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>80500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>83500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>79100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>74300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>68100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>53400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>49900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>54600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>56400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>58300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>55500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>18000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>15100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>14000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>13500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>13000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>13800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>12600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>12100</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6264,8 +6413,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6374,8 +6526,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6484,118 +6639,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>585100</v>
+      </c>
+      <c r="E66" s="3">
         <v>557600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>500300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>473600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>546000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>503200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>526400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>472900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>573600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>517100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>498200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>464000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>550300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>432600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>555500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>523200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>578500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>505900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>479900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>412000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>448600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>489900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>458400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>535100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>507500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>471800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>476500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>460300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>485200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>539800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>567200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>581200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>592700</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6634,8 +6795,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6744,8 +6906,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6854,8 +7019,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6964,8 +7132,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7074,118 +7245,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>779500</v>
+      </c>
+      <c r="E72" s="3">
         <v>721300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>681900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>630700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>614100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>561000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>504700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>454300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>438400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>359800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>317200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>279100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>268600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>296300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>250800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>204500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>178900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>106000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>53000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-33700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-96100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-147600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-181100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-189500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-194300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-215500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-237600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-240100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-265100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-281800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-300000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-296200</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7294,8 +7471,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7404,8 +7584,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7514,118 +7697,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>650300</v>
+      </c>
+      <c r="E76" s="3">
         <v>702600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>802700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>764300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>740100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>770000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>705900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>646900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>723600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>638800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>587200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>542600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>526500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>550700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>499900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>446400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>517800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>439600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>384100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>321300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>288400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>222600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>169000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>131600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>122000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>87900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>64000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>35500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>29000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-37200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-56800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-79000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-76200</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7734,233 +7923,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45654</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45290</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44562</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44380</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44289</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44198</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44009</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43918</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43827</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43736</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43645</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43554</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43463</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43372</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42917</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E81" s="3">
         <v>39400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>51200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>53200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>56300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>50400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>78600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>42700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>38100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-27700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>45500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>46300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>25700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>72900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>53000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>56200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>30500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>62400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>51400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>33500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>8500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>21300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>22200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>25200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>17000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>18800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>11300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>7000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7999,76 +8197,77 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12100</v>
+        <v>7200</v>
       </c>
       <c r="E83" s="3">
         <v>12100</v>
       </c>
       <c r="F83" s="3">
+        <v>12100</v>
+      </c>
+      <c r="G83" s="3">
         <v>11500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>8600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>7700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>7500</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>7700</v>
       </c>
       <c r="Z83" s="3">
         <v>7700</v>
@@ -8077,40 +8276,43 @@
         <v>7700</v>
       </c>
       <c r="AB83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AC83" s="3">
         <v>7400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>7300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>6500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>6600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>6300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>6200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>5800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>4600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8219,8 +8421,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8329,8 +8534,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8439,8 +8647,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8549,8 +8760,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8659,118 +8873,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>172900</v>
+      </c>
+      <c r="E89" s="3">
         <v>100900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>61200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-80300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>225600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>83500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>56000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-103700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>171200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>86000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>75500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-46700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>173100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>14000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-88600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>73300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>51000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>62500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-40300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>127300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>166700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>68500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>60300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>16800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>39800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>57200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>35200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>58300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>25300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>72200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>65600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>21600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-16100</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8809,118 +9029,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-12600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7500</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-8400</v>
       </c>
       <c r="AD91" s="3">
         <v>-8400</v>
       </c>
       <c r="AE91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9029,8 +9253,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9139,118 +9366,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-50200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-44400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-58000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-18700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-16100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-17800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-18100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-14800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-15000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-9500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-6200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9289,8 +9522,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9327,8 +9561,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9367,11 +9601,11 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-600</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -9399,8 +9633,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9509,8 +9746,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9619,8 +9859,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9729,205 +9972,211 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-127200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-153800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-33900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-101700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-102800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-107600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-7300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-7100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-102800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-53500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-52600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>45700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-12900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-21500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-45100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-37900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>18300</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
@@ -9938,125 +10187,131 @@
         <v>0</v>
       </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>100</v>
       </c>
-      <c r="AK101" s="3">
-        <v>0</v>
-      </c>
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-105200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-99800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>78300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>67500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>39000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-265000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>157600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>58200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>55300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-66900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>157000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-211900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>52900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>25500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>43500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-63000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>18500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>107300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>45700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>38000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>19000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-61000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>28000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>10900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>6800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>18900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>19400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>3800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-9700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/YETI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>YETI</t>
   </si>
@@ -656,507 +656,519 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E7" s="2">
         <v>46025</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45654</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45290</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44835</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44744</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44653</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44562</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44471</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44380</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44289</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44198</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44009</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43918</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43827</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43736</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43645</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43554</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43463</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43372</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43099</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42917</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>380400</v>
+      </c>
+      <c r="E8" s="3">
         <v>583700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>487800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>445900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>351100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>546500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>478400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>463500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>341400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>519800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>433600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>402600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>302800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>448000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>433600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>420000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>293600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>443100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>362600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>357700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>247600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>375800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>294600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>246900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>174400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>297600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>229100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>231700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>155400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>241200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>196100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>206300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>135300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>202100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>183000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>148400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>105700</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E9" s="3">
         <v>242800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>215200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>188300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>149400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>220100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>200700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>199200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>146600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>204600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>182300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>187700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>140900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>281000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>211100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>200900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>138800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>188300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>155600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>148600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>102400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>150900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>120600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>109400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>82000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>135300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>109000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>115400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>78700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>113400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>98600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>105700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>78100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>109000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>100800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>75400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>210200</v>
+      </c>
+      <c r="E10" s="3">
         <v>340900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>272500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>257600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>201700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>326400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>277700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>264300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>194800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>315200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>251300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>214800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>161900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>167000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>222500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>219100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>154800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>254800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>207000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>209200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>145200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>224900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>174000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>137500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>92400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>162300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>120100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>116300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>76700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>127800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>97500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>100600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>57200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>93100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>82200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>73000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>46300</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1196,41 +1208,42 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>25200</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>21100</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>15500</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1309,8 +1322,11 @@
       <c r="AM12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1422,38 +1438,41 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>-2000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1463,8 +1482,8 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1535,50 +1554,53 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E15" s="3">
         <v>33900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>29200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>29800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11400</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1648,8 +1670,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1686,234 +1711,241 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>368000</v>
+      </c>
+      <c r="E17" s="3">
         <v>509400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>433400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>383900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>329500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>466100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>408800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>396100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>313600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>421600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>371700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>352200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>287700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>491700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>365100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>351700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>260300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>349400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>293900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>285200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>207500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>294300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>224500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>200400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>158300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>285600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>195100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>196700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>146600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>203600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>168000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>173100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>132000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>178200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>158300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>130700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E18" s="3">
         <v>74300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>54400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>62000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>21700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>80500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>69600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>67400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>98200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>61900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>50300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-43700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>68500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>68300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>33300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>93700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>68700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>72500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>40100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>81500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>70100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>46500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>16200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>12000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>34000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>35000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>8800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>37600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>28100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>33200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>23900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>24700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>17700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1953,246 +1985,253 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>13500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>6500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-7300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-300</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-200</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>-100</v>
       </c>
       <c r="AI20" s="3">
         <v>-100</v>
       </c>
       <c r="AJ20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E21" s="3">
         <v>109400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>66900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>76000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>31100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>96100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>85800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>75300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>30800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>132200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>69000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>63400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>26500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-25900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>71200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>72400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>42800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>101700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>76000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>78900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>47300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>90300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>77500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>55100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>22000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>19200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>41100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>42300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>15400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>43200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>34200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>39300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>28900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>30600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>23500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E22" s="3">
         <v>400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2202,35 +2241,35 @@
       <c r="I22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>-700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>800</v>
       </c>
       <c r="T22" s="3">
         <v>800</v>
@@ -2242,284 +2281,293 @@
         <v>800</v>
       </c>
       <c r="W22" s="3">
+        <v>800</v>
+      </c>
+      <c r="X22" s="3">
         <v>900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>3100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>5300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>5700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>6800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>7800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>8400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>8100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E23" s="3">
         <v>75700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>53100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>68100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>69100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>74100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>67300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>22400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>103000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>57600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>50800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-38500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>59700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>61600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>33400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>92200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>66700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>70600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>38900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>81100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>68100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>44800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>11200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>28400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>29400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>29900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>20200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>24500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-4900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>14700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>16500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>10900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E24" s="3">
         <v>17500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>16900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>17800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>16900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>24400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>19300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>14400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>8400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>18800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>16600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>11300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2000</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>7100</v>
       </c>
       <c r="AD24" s="3">
         <v>7100</v>
       </c>
       <c r="AE24" s="3">
+        <v>7100</v>
+      </c>
+      <c r="AF24" s="3">
         <v>600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>5000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>5200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>3800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2631,234 +2679,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E26" s="3">
         <v>58200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>39400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>51200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>53200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>56300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>50400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>78600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>42700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>38100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>45500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>46300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>25700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>72900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>53000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>56200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>30500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>62400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>51400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>33500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>8500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>21300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>22200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>25200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>17000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>18800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>9700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>11300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>7100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E27" s="3">
         <v>58200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>39400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>51200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>53200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>56300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>50400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>15900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>78600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>42700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>38100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>45500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>46300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>25700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>72900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>53000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>56200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>30500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>62400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>51400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>33500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>8500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>21300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>22200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>25200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>17000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>18800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>9700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>11300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>7000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2970,8 +3027,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3053,17 +3113,17 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3071,20 +3131,23 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-5700</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3196,8 +3259,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3309,234 +3375,243 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-13500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>7300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>300</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>200</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>100</v>
       </c>
       <c r="AI32" s="3">
         <v>100</v>
       </c>
       <c r="AJ32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK32" s="3">
         <v>600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E33" s="3">
         <v>58200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>39400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>51200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>53200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>56300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>50400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>78600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>42700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>38100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>45500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>46300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>25700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>72900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>53000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>56200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>30500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>62400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>51400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>33500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>8500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>21300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>22200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>25200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>17000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>18800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>11300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>7000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3648,239 +3723,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E35" s="3">
         <v>58200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>39400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>51200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>53200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>56300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>50400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>78600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>42700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>38100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>45500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>46300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>25700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>72900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>53000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>56200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>30500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>62400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>51400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>33500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>8500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>21300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>22200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>25200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>17000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>18800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>11300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>7000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E38" s="2">
         <v>46025</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45654</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45290</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44835</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44744</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44653</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44562</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44471</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44380</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44289</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44198</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44009</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43918</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43827</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43736</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43645</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43554</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43463</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43372</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43099</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42917</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3920,8 +4004,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3961,121 +4046,125 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>127800</v>
+      </c>
+      <c r="E41" s="3">
         <v>188300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>164500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>269700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>259000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>358800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>280500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>212900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>173900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>439000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>281400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>223100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>167800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>234700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>77800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>92000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>100300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>312200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>259300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>233800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>190300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>253300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>234800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>127500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>118200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>72500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>34600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>38000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>19000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>80100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>52100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>71300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>60400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>53700</v>
       </c>
-      <c r="AK41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4187,460 +4276,475 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E43" s="3">
         <v>141400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>157400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>163600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>120500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>120200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>143700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>159100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>108400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>95800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>127900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>131600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>95600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>79400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>93900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>94300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>83000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>109500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>83300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>81900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>67100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>65400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>71200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>85900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>60200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>82700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>74800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>75900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>63000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>59300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>61900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>65400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>60400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>67200</v>
       </c>
-      <c r="AK43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>318400</v>
+      </c>
+      <c r="E44" s="3">
         <v>290600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>324000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>342100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>330500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>310100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>370200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>378300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>363900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>337200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>341300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>322000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>347000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>371400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>439400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>490000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>413000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>318900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>266000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>221700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>183900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>140100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>134600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>138800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>202400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>185700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>209200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>181400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>164300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>145400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>157700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>149400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>158500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>175100</v>
       </c>
-      <c r="AK44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E45" s="3">
         <v>10000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>33300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>33600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>40800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>39600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>29600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>23800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>24500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>17700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>15300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>19900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>19600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>13300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>17800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>20100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>12200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>13000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>11100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>7100</v>
       </c>
-      <c r="AK45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>642300</v>
+      </c>
+      <c r="E46" s="3">
         <v>660300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>696700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>828200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>767200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>826800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>846300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>807200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>703200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>914400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>791300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>721900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>654900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>718900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>644700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>717000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>635900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>770200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>632200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>561200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>465700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>476500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>454700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>367400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>400600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>360500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>331800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>313000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>266400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>297000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>284600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>297300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>289900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>303000</v>
       </c>
-      <c r="AK46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4680,8 +4784,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4752,234 +4856,243 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>270200</v>
+      </c>
+      <c r="E48" s="3">
         <v>273600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>268700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>223000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>219600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>204500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>213000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>212300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>207100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>208300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>192600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>189500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>179300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>180000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>183700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>183800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>179700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>174000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>163000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>153700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>119100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>112200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>110000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>112300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>116300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>120400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>81200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>80000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>78200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>74100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>72400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>71100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>71500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>73800</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>296200</v>
+      </c>
+      <c r="E49" s="3">
         <v>292100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>286100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>248500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>246500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>244600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>210800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>209800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>206800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>171900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>168400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>165200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>155100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>153700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>152400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>152100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>151400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>149600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>148400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>147200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>146500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>146400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>145900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>145800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>145700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>145100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>145000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>144700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>144300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>134300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>135400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>133700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>130300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>128600</v>
       </c>
-      <c r="AK49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5091,8 +5204,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5204,121 +5320,127 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E52" s="3">
         <v>9400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8700</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1200</v>
       </c>
       <c r="G52" s="3">
         <v>1200</v>
       </c>
       <c r="H52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I52" s="3">
         <v>10200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>3000</v>
       </c>
       <c r="J52" s="3">
         <v>3000</v>
       </c>
       <c r="K52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L52" s="3">
         <v>2700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2600</v>
-      </c>
-      <c r="M52" s="3">
-        <v>900</v>
       </c>
       <c r="N52" s="3">
         <v>900</v>
       </c>
       <c r="O52" s="3">
+        <v>900</v>
+      </c>
+      <c r="P52" s="3">
         <v>17300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2400</v>
-      </c>
-      <c r="R52" s="3">
-        <v>2500</v>
       </c>
       <c r="S52" s="3">
         <v>2500</v>
       </c>
       <c r="T52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="U52" s="3">
         <v>2600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1900</v>
-      </c>
-      <c r="X52" s="3">
-        <v>2000</v>
       </c>
       <c r="Y52" s="3">
         <v>2000</v>
       </c>
       <c r="Z52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA52" s="3">
         <v>1900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>10100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>8300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>10600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>11000</v>
       </c>
-      <c r="AK52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL52" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5430,121 +5552,127 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1218600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1235400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1260100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1303000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1237900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1286100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1273200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1232300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1119800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1297200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1155900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1085400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1006500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1076800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>983200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1055400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>969500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1096400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>945500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>864000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>733300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>737100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>712600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>627500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>666800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>629500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>559700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>540400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>495800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>514200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>502600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>510400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>502200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>516400</v>
       </c>
-      <c r="AK54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5584,8 +5712,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5625,168 +5754,172 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>146600</v>
+      </c>
+      <c r="E57" s="3">
         <v>140200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>146700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>152300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>137600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>158500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>148200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>175200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>139100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>190400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>179100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>143400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>101700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>140800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>122800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>204100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>167400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>191300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>166100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>145700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>120000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>123600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>101900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>41400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>74400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>83800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>105500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>101500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>78200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>68700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>76900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>73500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>51600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>40300</v>
       </c>
-      <c r="AK57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E58" s="3">
         <v>20200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21900</v>
-      </c>
-      <c r="F58" s="3">
-        <v>27400</v>
       </c>
       <c r="G58" s="3">
         <v>27400</v>
       </c>
       <c r="H58" s="3">
+        <v>27400</v>
+      </c>
+      <c r="I58" s="3">
         <v>26100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>23700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>22800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>22100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>21300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>19900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>17900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>35700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>24600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>24400</v>
-      </c>
-      <c r="R58" s="3">
-        <v>24600</v>
       </c>
       <c r="S58" s="3">
         <v>24600</v>
@@ -5795,43 +5928,43 @@
         <v>24600</v>
       </c>
       <c r="U58" s="3">
-        <v>24500</v>
+        <v>24600</v>
       </c>
       <c r="V58" s="3">
         <v>24500</v>
       </c>
       <c r="W58" s="3">
-        <v>22700</v>
+        <v>24500</v>
       </c>
       <c r="X58" s="3">
         <v>22700</v>
       </c>
       <c r="Y58" s="3">
+        <v>22700</v>
+      </c>
+      <c r="Z58" s="3">
         <v>20800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>18900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>17100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>15200</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>42100</v>
       </c>
       <c r="AD58" s="3">
         <v>42100</v>
       </c>
       <c r="AE58" s="3">
-        <v>43600</v>
+        <v>42100</v>
       </c>
       <c r="AF58" s="3">
         <v>43600</v>
       </c>
       <c r="AG58" s="3">
-        <v>47100</v>
+        <v>43600</v>
       </c>
       <c r="AH58" s="3">
         <v>47100</v>
@@ -5842,8 +5975,8 @@
       <c r="AJ58" s="3">
         <v>47100</v>
       </c>
-      <c r="AK58" s="3" t="s">
-        <v>8</v>
+      <c r="AK58" s="3">
+        <v>47100</v>
       </c>
       <c r="AL58" s="3" t="s">
         <v>8</v>
@@ -5851,460 +5984,475 @@
       <c r="AM58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>61700</v>
+        <v>10100</v>
       </c>
       <c r="E59" s="3">
+        <v>77600</v>
+      </c>
+      <c r="F59" s="3">
         <v>74800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>74200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>70500</v>
       </c>
-      <c r="H59" s="3">
-        <v>61900</v>
-      </c>
       <c r="I59" s="3">
+        <v>100000</v>
+      </c>
+      <c r="J59" s="3">
         <v>73700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>73500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>79800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>96700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>83100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>118200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>92900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>243600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>128400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>162700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>158100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>187800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>139200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>133800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>110300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>141400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>96900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>70800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>59100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>71300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>53400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>54500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>50600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>75000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>62100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>52100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>51900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>64500</v>
       </c>
-      <c r="AK59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>305600</v>
+      </c>
+      <c r="E60" s="3">
         <v>334300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>322000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>329000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>297200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>379500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>328100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>351900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>298800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>398400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>360800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>344900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>329800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>409000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>275600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>391400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>350100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>403700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>329900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>304000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>253000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>287800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>219600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>131200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>150600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>170300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>201100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>198200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>172500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>187300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>186000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>172600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>150600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>151900</v>
       </c>
-      <c r="AK60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>204800</v>
+      </c>
+      <c r="E61" s="3">
         <v>208200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>200700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>149600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>155700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>146400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>154300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>154000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>152800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>154800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>139700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>138400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>119900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>71700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>77800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>83600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>89600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>95700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>101700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>107800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>105500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>111000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>215800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>270800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>326300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>281700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>252700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>263300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>273800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>284400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>340700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>380800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>418000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>428600</v>
       </c>
-      <c r="AK61" s="3">
-        <v>0</v>
-      </c>
       <c r="AL61" s="3">
         <v>0</v>
       </c>
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E62" s="3">
         <v>20300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>22000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>21800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>19800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>19500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>18300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>69500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>79200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>80500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>83500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>79100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>74300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>68100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>53400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>49900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>54600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>56400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>58300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>55500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>18000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>15100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>14000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>13500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>13000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>13800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>12600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>12100</v>
       </c>
-      <c r="AK62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM62" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN62" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6416,8 +6564,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6529,8 +6680,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6642,121 +6796,127 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>558700</v>
+      </c>
+      <c r="E66" s="3">
         <v>585100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>557600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>500300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>473600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>546000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>503200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>526400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>472900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>573600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>517100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>498200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>464000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>550300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>432600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>555500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>523200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>578500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>505900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>479900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>412000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>448600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>489900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>458400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>535100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>507500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>471800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>476500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>460300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>485200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>539800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>567200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>581200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>592700</v>
       </c>
-      <c r="AK66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6796,8 +6956,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6909,8 +7070,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7022,8 +7186,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7135,8 +7302,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7248,121 +7418,127 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>789400</v>
+      </c>
+      <c r="E72" s="3">
         <v>779500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>721300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>681900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>630700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>614100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>561000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>504700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>454300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>438400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>359800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>317200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>279100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>268600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>296300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>250800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>204500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>178900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>106000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>53000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-33700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-96100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-147600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-181100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-189500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-194300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-215500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-237600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-240100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-265100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-281800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-300000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-296200</v>
       </c>
-      <c r="AK72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7474,8 +7650,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7587,8 +7766,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7700,121 +7882,127 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>659900</v>
+      </c>
+      <c r="E76" s="3">
         <v>650300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>702600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>802700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>764300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>740100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>770000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>705900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>646900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>723600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>638800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>587200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>542600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>526500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>550700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>499900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>446400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>517800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>439600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>384100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>321300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>288400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>222600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>169000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>131600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>122000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>87900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>64000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>35500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>29000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-37200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-56800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-79000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-76200</v>
       </c>
-      <c r="AK76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7926,239 +8114,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E80" s="2">
         <v>46025</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45654</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45290</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44835</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44744</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44653</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44562</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44471</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44380</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44289</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44198</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44009</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43918</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43827</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43736</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43645</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43554</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43463</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43372</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43099</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42917</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42826</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E81" s="3">
         <v>58200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>39400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>51200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>53200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>56300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>50400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>78600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>42700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>38100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>45500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>46300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>25700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>72900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>53000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>56200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>30500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>62400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>51400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>33500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>8500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>21300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>22200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>25200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>17000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>18800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>11300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>7000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-6900</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8198,79 +8395,80 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E83" s="3">
         <v>7200</v>
-      </c>
-      <c r="E83" s="3">
-        <v>12100</v>
       </c>
       <c r="F83" s="3">
         <v>12100</v>
       </c>
       <c r="G83" s="3">
+        <v>12100</v>
+      </c>
+      <c r="H83" s="3">
         <v>11500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>9800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>9800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>8700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>8500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>7600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>7700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>7500</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>7700</v>
       </c>
       <c r="AA83" s="3">
         <v>7700</v>
@@ -8279,40 +8477,43 @@
         <v>7700</v>
       </c>
       <c r="AC83" s="3">
+        <v>7700</v>
+      </c>
+      <c r="AD83" s="3">
         <v>7400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>7300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>6500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>6600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>6300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>6200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>5600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>5800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>4600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8424,8 +8625,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8537,8 +8741,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8650,8 +8857,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8763,8 +8973,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8876,121 +9089,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E89" s="3">
         <v>172900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>100900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>61200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-80300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>225600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>83500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>56000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-103700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>171200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>86000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>75500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-46700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>173100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>14000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-88600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>73300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>51000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>62500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-40300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>127300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>166700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>68500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>60300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>16800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>39800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>57200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>35200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>58300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>25300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>72200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>65600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>21600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-16100</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9030,121 +9249,125 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-12600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-7500</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-8400</v>
       </c>
       <c r="AE91" s="3">
         <v>-8400</v>
       </c>
       <c r="AF91" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-9600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9256,8 +9479,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9369,121 +9595,127 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-50200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-44400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-58000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-15700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-16100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-17800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-18100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-14800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-9500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-9500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-6200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9523,8 +9755,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9564,8 +9797,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9604,11 +9837,11 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-600</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -9636,8 +9869,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9749,8 +9985,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9862,8 +10101,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9975,211 +10217,217 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-127200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-153800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-33900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-101700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-102800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-107600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-7300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-7100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-102800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-53500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-52600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>45700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-12900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-21500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-45100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-37900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>18300</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
         <v>0</v>
       </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
         <v>0</v>
       </c>
@@ -10190,128 +10438,134 @@
         <v>0</v>
       </c>
       <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
         <v>-100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>100</v>
       </c>
-      <c r="AL101" s="3">
-        <v>0</v>
-      </c>
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-60600</v>
+      </c>
+      <c r="E102" s="3">
         <v>23900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-105200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-99800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>78300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>67500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>39000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-265000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>157600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>58200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>55300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-66900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>157000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-14200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-211900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>52900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>25500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>43500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-63000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>18500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>107300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>9200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>45700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>38000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>19000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-61000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>28000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-19200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>10900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>18900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>19400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>3800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-9700</v>
       </c>
     </row>
